--- a/data/metadata_raw/fixed_capital_investment_per_capita.xlsx
+++ b/data/metadata_raw/fixed_capital_investment_per_capita.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1237">
   <si>
     <t>Code</t>
   </si>
@@ -2852,6 +2852,9 @@
     <t>Бухоро тумани</t>
   </si>
   <si>
+    <t>Вобкент тумани</t>
+  </si>
+  <si>
     <t>Ғиждувон тумани</t>
   </si>
   <si>
@@ -3596,7 +3599,7 @@
     <t>2022-08-10</t>
   </si>
   <si>
-    <t>2024-08-09</t>
+    <t>2026-03-05</t>
   </si>
   <si>
     <t>1.04.01.0006</t>
@@ -4204,7 +4207,7 @@
         <v>9778.799999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>13652.7</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -4266,7 +4269,7 @@
         <v>6514.1</v>
       </c>
       <c r="T3">
-        <v>10201.21540521774</v>
+        <v>10201.2</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4328,7 +4331,7 @@
         <v>8988.200000000001</v>
       </c>
       <c r="T4">
-        <v>9889.155016086575</v>
+        <v>9889.200000000001</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4390,7 +4393,7 @@
         <v>1820.8</v>
       </c>
       <c r="T5">
-        <v>2791.051425899953</v>
+        <v>2791.1</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -4452,7 +4455,7 @@
         <v>1723.5</v>
       </c>
       <c r="T6">
-        <v>2739.786093674553</v>
+        <v>2739.8</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -4514,7 +4517,7 @@
         <v>4752.1</v>
       </c>
       <c r="T7">
-        <v>2916.082191780822</v>
+        <v>2916.1</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -4576,7 +4579,7 @@
         <v>51911.1</v>
       </c>
       <c r="T8">
-        <v>119576.0238095238</v>
+        <v>119576</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -4638,7 +4641,7 @@
         <v>1699.9</v>
       </c>
       <c r="T9">
-        <v>1579.809587217044</v>
+        <v>1579.8</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -4700,7 +4703,7 @@
         <v>16446.6</v>
       </c>
       <c r="T10">
-        <v>35550.20131771596</v>
+        <v>35550.2</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -4762,7 +4765,7 @@
         <v>3143.5</v>
       </c>
       <c r="T11">
-        <v>4530.042513863216</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -4824,7 +4827,7 @@
         <v>36170.7</v>
       </c>
       <c r="T12">
-        <v>52070.7002967359</v>
+        <v>52070.7</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -4886,7 +4889,7 @@
         <v>6337.6</v>
       </c>
       <c r="T13">
-        <v>4873.338235294117</v>
+        <v>4873.3</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -4948,7 +4951,7 @@
         <v>1395.5</v>
       </c>
       <c r="T14">
-        <v>2281.587548638133</v>
+        <v>2281.6</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -5010,7 +5013,7 @@
         <v>2778.4</v>
       </c>
       <c r="T15">
-        <v>3293.470437017995</v>
+        <v>3293.5</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -5072,7 +5075,7 @@
         <v>3205.8</v>
       </c>
       <c r="T16">
-        <v>2495.45186470078</v>
+        <v>2495.5</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -5134,7 +5137,7 @@
         <v>2496.9</v>
       </c>
       <c r="T17">
-        <v>2294.725656877898</v>
+        <v>2294.7</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -5196,7 +5199,7 @@
         <v>2549.4</v>
       </c>
       <c r="T18">
-        <v>3723.884582256675</v>
+        <v>3723.9</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -5258,7 +5261,7 @@
         <v>2121.2</v>
       </c>
       <c r="T19">
-        <v>2381.118353344769</v>
+        <v>2381.1</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -5320,7 +5323,7 @@
         <v>3111.1</v>
       </c>
       <c r="T20">
-        <v>2562.977971014493</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -5382,7 +5385,7 @@
         <v>5549.8</v>
       </c>
       <c r="T21">
-        <v>8363.617994573622</v>
+        <v>8363.6</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -5444,7 +5447,7 @@
         <v>7325.2</v>
       </c>
       <c r="T22">
-        <v>7069.421701602958</v>
+        <v>7069.4</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -5506,7 +5509,7 @@
         <v>4317.3</v>
       </c>
       <c r="T23">
-        <v>16884.19480519481</v>
+        <v>16884.2</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -5568,7 +5571,7 @@
         <v>3550.5</v>
       </c>
       <c r="T24">
-        <v>7364.3033126294</v>
+        <v>7364.3</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -5630,7 +5633,7 @@
         <v>3656.4</v>
       </c>
       <c r="T25">
-        <v>12982.42343587971</v>
+        <v>12982.4</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -5692,7 +5695,7 @@
         <v>3311.5</v>
       </c>
       <c r="T26">
-        <v>6417.46743119266</v>
+        <v>6417.5</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -5754,7 +5757,7 @@
         <v>2526</v>
       </c>
       <c r="T27">
-        <v>11251.98096446701</v>
+        <v>11252</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -5816,7 +5819,7 @@
         <v>42707.5</v>
       </c>
       <c r="T28">
-        <v>31599.54045307443</v>
+        <v>31599.5</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -5878,7 +5881,7 @@
         <v>3319.2</v>
       </c>
       <c r="T29">
-        <v>4465.977045908183</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -5940,7 +5943,7 @@
         <v>1374.9</v>
       </c>
       <c r="T30">
-        <v>3264.998836307215</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -6002,7 +6005,7 @@
         <v>4252.5</v>
       </c>
       <c r="T31">
-        <v>12124.80031201248</v>
+        <v>12124.8</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -6064,7 +6067,7 @@
         <v>3443.5</v>
       </c>
       <c r="T32">
-        <v>4354.234939759036</v>
+        <v>4354.2</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -6126,7 +6129,7 @@
         <v>3096.8</v>
       </c>
       <c r="T33">
-        <v>11774.10460251046</v>
+        <v>11774.1</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -6188,7 +6191,7 @@
         <v>2860.1</v>
       </c>
       <c r="T34">
-        <v>7376.774056353003</v>
+        <v>7376.8</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -6250,7 +6253,7 @@
         <v>2376.1</v>
       </c>
       <c r="T35">
-        <v>2686.247636474535</v>
+        <v>2686.2</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -6312,7 +6315,7 @@
         <v>2663.6</v>
       </c>
       <c r="T36">
-        <v>4818.743236829616</v>
+        <v>4818.7</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -6374,7 +6377,7 @@
         <v>7588.4</v>
       </c>
       <c r="T37">
-        <v>8836.729372937294</v>
+        <v>8836.700000000001</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -6436,7 +6439,7 @@
         <v>15309.4</v>
       </c>
       <c r="T38">
-        <v>25073.47721426838</v>
+        <v>25073.5</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -6498,7 +6501,7 @@
         <v>15933.9</v>
       </c>
       <c r="T39">
-        <v>23461.55480833894</v>
+        <v>23461.6</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -6560,7 +6563,7 @@
         <v>6003</v>
       </c>
       <c r="T40">
-        <v>4489.181259600615</v>
+        <v>4489.2</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -6622,7 +6625,7 @@
         <v>9781.6</v>
       </c>
       <c r="T41">
-        <v>20792.19523809524</v>
+        <v>20792.2</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -6684,7 +6687,7 @@
         <v>11748.9</v>
       </c>
       <c r="T42">
-        <v>21213.79622431982</v>
+        <v>21213.8</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -6701,7 +6704,7 @@
         <v>724</v>
       </c>
       <c r="E43" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F43">
         <v>193.9</v>
@@ -6746,7 +6749,7 @@
         <v>6429.6</v>
       </c>
       <c r="T43">
-        <v>6608.237333333333</v>
+        <v>6608.2</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -6763,7 +6766,7 @@
         <v>725</v>
       </c>
       <c r="E44" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F44">
         <v>242.9</v>
@@ -6808,7 +6811,7 @@
         <v>14774</v>
       </c>
       <c r="T44">
-        <v>24354.73384615385</v>
+        <v>24354.7</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -6825,7 +6828,7 @@
         <v>726</v>
       </c>
       <c r="E45" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F45">
         <v>1410.2</v>
@@ -6870,7 +6873,7 @@
         <v>21234.5</v>
       </c>
       <c r="T45">
-        <v>21299.25263157895</v>
+        <v>21299.3</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -6887,7 +6890,7 @@
         <v>727</v>
       </c>
       <c r="E46" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F46">
         <v>164.1</v>
@@ -6932,7 +6935,7 @@
         <v>15816.2</v>
       </c>
       <c r="T46">
-        <v>75869.29768786127</v>
+        <v>75869.3</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -6949,7 +6952,7 @@
         <v>728</v>
       </c>
       <c r="E47" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F47">
         <v>6452.7</v>
@@ -6994,7 +6997,7 @@
         <v>185744.4</v>
       </c>
       <c r="T47">
-        <v>195521.7611940298</v>
+        <v>195521.8</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -7011,7 +7014,7 @@
         <v>729</v>
       </c>
       <c r="E48" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F48">
         <v>221.3</v>
@@ -7056,7 +7059,7 @@
         <v>31691</v>
       </c>
       <c r="T48">
-        <v>43316.33182161753</v>
+        <v>43316.3</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -7073,7 +7076,7 @@
         <v>730</v>
       </c>
       <c r="E49" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F49">
         <v>1340.6</v>
@@ -7118,7 +7121,7 @@
         <v>27000.2</v>
       </c>
       <c r="T49">
-        <v>22885.73031496063</v>
+        <v>22885.7</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -7135,7 +7138,7 @@
         <v>731</v>
       </c>
       <c r="E50" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F50">
         <v>180.7</v>
@@ -7180,7 +7183,7 @@
         <v>3024.2</v>
       </c>
       <c r="T50">
-        <v>3230.769764957265</v>
+        <v>3230.8</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -7197,7 +7200,7 @@
         <v>732</v>
       </c>
       <c r="E51" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F51">
         <v>150.6</v>
@@ -7242,7 +7245,7 @@
         <v>1993.1</v>
       </c>
       <c r="T51">
-        <v>4183.993062966916</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -7259,7 +7262,7 @@
         <v>733</v>
       </c>
       <c r="E52" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F52">
         <v>391.5</v>
@@ -7304,7 +7307,7 @@
         <v>10037.4</v>
       </c>
       <c r="T52">
-        <v>15445.27257799672</v>
+        <v>15445.3</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -7321,7 +7324,7 @@
         <v>734</v>
       </c>
       <c r="E53" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F53">
         <v>750.6</v>
@@ -7366,7 +7369,7 @@
         <v>17947.9</v>
       </c>
       <c r="T53">
-        <v>23300.59322890349</v>
+        <v>23300.6</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -7383,7 +7386,7 @@
         <v>735</v>
       </c>
       <c r="E54" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F54">
         <v>641.7</v>
@@ -7428,7 +7431,7 @@
         <v>4044.9</v>
       </c>
       <c r="T54">
-        <v>12094.71079429735</v>
+        <v>12094.7</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -7445,7 +7448,7 @@
         <v>736</v>
       </c>
       <c r="E55" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F55">
         <v>216.2</v>
@@ -7490,7 +7493,7 @@
         <v>2901.6</v>
       </c>
       <c r="T55">
-        <v>4862.201856148492</v>
+        <v>4862.2</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -7507,7 +7510,7 @@
         <v>737</v>
       </c>
       <c r="E56" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F56">
         <v>264.2</v>
@@ -7552,7 +7555,7 @@
         <v>17568.7</v>
       </c>
       <c r="T56">
-        <v>12463.94647588765</v>
+        <v>12463.9</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -7569,7 +7572,7 @@
         <v>738</v>
       </c>
       <c r="E57" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F57">
         <v>211.2</v>
@@ -7614,7 +7617,7 @@
         <v>6527.7</v>
       </c>
       <c r="T57">
-        <v>22929.06951219512</v>
+        <v>22929.1</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -7631,7 +7634,7 @@
         <v>739</v>
       </c>
       <c r="E58" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F58">
         <v>291.2</v>
@@ -7676,7 +7679,7 @@
         <v>3243.4</v>
       </c>
       <c r="T58">
-        <v>9094.224431818182</v>
+        <v>9094.200000000001</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -7693,7 +7696,7 @@
         <v>740</v>
       </c>
       <c r="E59" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F59">
         <v>245.9</v>
@@ -7738,7 +7741,7 @@
         <v>4495.7</v>
       </c>
       <c r="T59">
-        <v>12742.57182168409</v>
+        <v>12742.6</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -7755,7 +7758,7 @@
         <v>741</v>
       </c>
       <c r="E60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F60">
         <v>228.1</v>
@@ -7800,7 +7803,7 @@
         <v>2715.5</v>
       </c>
       <c r="T60">
-        <v>4978.475392670157</v>
+        <v>4978.5</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -7817,7 +7820,7 @@
         <v>742</v>
       </c>
       <c r="E61" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F61">
         <v>181.1</v>
@@ -7862,7 +7865,7 @@
         <v>7634</v>
       </c>
       <c r="T61">
-        <v>15983.73345259392</v>
+        <v>15983.7</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -7879,7 +7882,7 @@
         <v>743</v>
       </c>
       <c r="E62" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F62">
         <v>243.4</v>
@@ -7924,7 +7927,7 @@
         <v>6829.1</v>
       </c>
       <c r="T62">
-        <v>24217.24214417745</v>
+        <v>24217.2</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -7941,7 +7944,7 @@
         <v>744</v>
       </c>
       <c r="E63" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F63">
         <v>200.2</v>
@@ -7986,7 +7989,7 @@
         <v>3510.5</v>
       </c>
       <c r="T63">
-        <v>6767.959608323133</v>
+        <v>6768</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -8003,7 +8006,7 @@
         <v>745</v>
       </c>
       <c r="E64" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F64">
         <v>232.7</v>
@@ -8048,7 +8051,7 @@
         <v>34987.8</v>
       </c>
       <c r="T64">
-        <v>31791.51765893038</v>
+        <v>31791.5</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -8065,7 +8068,7 @@
         <v>746</v>
       </c>
       <c r="E65" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F65">
         <v>347.8</v>
@@ -8110,7 +8113,7 @@
         <v>7957.5</v>
       </c>
       <c r="T65">
-        <v>4717.336666666667</v>
+        <v>4717.3</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -8127,7 +8130,7 @@
         <v>747</v>
       </c>
       <c r="E66" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F66">
         <v>678.5</v>
@@ -8172,7 +8175,7 @@
         <v>6002.6</v>
       </c>
       <c r="T66">
-        <v>9856.257888888889</v>
+        <v>9856.299999999999</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -8189,7 +8192,7 @@
         <v>748</v>
       </c>
       <c r="E67" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F67">
         <v>1113.1</v>
@@ -8234,7 +8237,7 @@
         <v>11337.6</v>
       </c>
       <c r="T67">
-        <v>15328.78403755869</v>
+        <v>15328.8</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -8251,7 +8254,7 @@
         <v>749</v>
       </c>
       <c r="E68" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8296,7 +8299,7 @@
         <v>2212.6</v>
       </c>
       <c r="T68">
-        <v>5804.397444519167</v>
+        <v>5804.4</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -8313,7 +8316,7 @@
         <v>750</v>
       </c>
       <c r="E69" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -8358,7 +8361,7 @@
         <v>1656</v>
       </c>
       <c r="T69">
-        <v>2519.899791231733</v>
+        <v>2519.9</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -8375,7 +8378,7 @@
         <v>751</v>
       </c>
       <c r="E70" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F70">
         <v>1180.1</v>
@@ -8420,7 +8423,7 @@
         <v>12055.8</v>
       </c>
       <c r="T70">
-        <v>15258.99243098842</v>
+        <v>15259</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -8437,7 +8440,7 @@
         <v>752</v>
       </c>
       <c r="E71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F71">
         <v>1029.4</v>
@@ -8482,7 +8485,7 @@
         <v>2113.2</v>
       </c>
       <c r="T71">
-        <v>3248.055245189324</v>
+        <v>3248.1</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -8499,7 +8502,7 @@
         <v>753</v>
       </c>
       <c r="E72" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F72">
         <v>100.9</v>
@@ -8544,7 +8547,7 @@
         <v>1536.1</v>
       </c>
       <c r="T72">
-        <v>1706.3173693086</v>
+        <v>1706.3</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -8561,7 +8564,7 @@
         <v>754</v>
       </c>
       <c r="E73" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F73">
         <v>242.5</v>
@@ -8606,7 +8609,7 @@
         <v>2745.6</v>
       </c>
       <c r="T73">
-        <v>2752.472806381436</v>
+        <v>2752.5</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -8623,7 +8626,7 @@
         <v>755</v>
       </c>
       <c r="E74" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F74">
         <v>201</v>
@@ -8668,7 +8671,7 @@
         <v>2023.8</v>
       </c>
       <c r="T74">
-        <v>1539.323091542604</v>
+        <v>1539.3</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -8685,7 +8688,7 @@
         <v>756</v>
       </c>
       <c r="E75" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F75">
         <v>132.8</v>
@@ -8730,7 +8733,7 @@
         <v>2554.7</v>
       </c>
       <c r="T75">
-        <v>3845.106039325842</v>
+        <v>3845.1</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -8747,7 +8750,7 @@
         <v>757</v>
       </c>
       <c r="E76" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F76">
         <v>2779.7</v>
@@ -8792,7 +8795,7 @@
         <v>3186.7</v>
       </c>
       <c r="T76">
-        <v>4061.792207792208</v>
+        <v>4061.8</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -8809,7 +8812,7 @@
         <v>758</v>
       </c>
       <c r="E77" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F77">
         <v>6245.5</v>
@@ -8854,7 +8857,7 @@
         <v>44094.7</v>
       </c>
       <c r="T77">
-        <v>63529.69141039237</v>
+        <v>63529.7</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -8871,7 +8874,7 @@
         <v>759</v>
       </c>
       <c r="E78" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F78">
         <v>759</v>
@@ -8916,7 +8919,7 @@
         <v>27274.7</v>
       </c>
       <c r="T78">
-        <v>76882.36239620404</v>
+        <v>76882.39999999999</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -8933,7 +8936,7 @@
         <v>760</v>
       </c>
       <c r="E79" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F79">
         <v>153.8</v>
@@ -8978,7 +8981,7 @@
         <v>4072.4</v>
       </c>
       <c r="T79">
-        <v>3859.627205199628</v>
+        <v>3859.6</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -8995,7 +8998,7 @@
         <v>761</v>
       </c>
       <c r="E80" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F80">
         <v>83.3</v>
@@ -9040,7 +9043,7 @@
         <v>2579.3</v>
       </c>
       <c r="T80">
-        <v>2745.594026548672</v>
+        <v>2745.6</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -9057,7 +9060,7 @@
         <v>762</v>
       </c>
       <c r="E81" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F81">
         <v>191.8</v>
@@ -9102,7 +9105,7 @@
         <v>1978.7</v>
       </c>
       <c r="T81">
-        <v>4003.466694772344</v>
+        <v>4003.5</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -9119,7 +9122,7 @@
         <v>763</v>
       </c>
       <c r="E82" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F82">
         <v>194.4</v>
@@ -9164,7 +9167,7 @@
         <v>2524.4</v>
       </c>
       <c r="T82">
-        <v>2657.762438682551</v>
+        <v>2657.8</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -9181,7 +9184,7 @@
         <v>764</v>
       </c>
       <c r="E83" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F83">
         <v>2031</v>
@@ -9226,7 +9229,7 @@
         <v>24778.1</v>
       </c>
       <c r="T83">
-        <v>30921.82294930876</v>
+        <v>30921.8</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -9243,7 +9246,7 @@
         <v>765</v>
       </c>
       <c r="E84" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F84">
         <v>1129.1</v>
@@ -9288,7 +9291,7 @@
         <v>33859.5</v>
       </c>
       <c r="T84">
-        <v>34173.69066503966</v>
+        <v>34173.7</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -9305,7 +9308,7 @@
         <v>766</v>
       </c>
       <c r="E85" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F85">
         <v>2037.3</v>
@@ -9350,7 +9353,7 @@
         <v>45145.8</v>
       </c>
       <c r="T85">
-        <v>13149.83668903803</v>
+        <v>13149.8</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -9367,7 +9370,7 @@
         <v>767</v>
       </c>
       <c r="E86" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9412,7 +9415,7 @@
         <v>40550.1</v>
       </c>
       <c r="T86">
-        <v>35087.23655913978</v>
+        <v>35087.2</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -9429,7 +9432,7 @@
         <v>768</v>
       </c>
       <c r="E87" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F87">
         <v>239.5</v>
@@ -9474,7 +9477,7 @@
         <v>27953.7</v>
       </c>
       <c r="T87">
-        <v>30216.44772117963</v>
+        <v>30216.4</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -9491,7 +9494,7 @@
         <v>769</v>
       </c>
       <c r="E88" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F88">
         <v>240.6</v>
@@ -9536,7 +9539,7 @@
         <v>6849.5</v>
       </c>
       <c r="T88">
-        <v>6451.462009803922</v>
+        <v>6451.5</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -9553,7 +9556,7 @@
         <v>770</v>
       </c>
       <c r="E89" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F89">
         <v>306.4</v>
@@ -9598,7 +9601,7 @@
         <v>6248.8</v>
       </c>
       <c r="T89">
-        <v>6170.958915365653</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -9615,7 +9618,7 @@
         <v>771</v>
       </c>
       <c r="E90" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F90">
         <v>1824.9</v>
@@ -9660,7 +9663,7 @@
         <v>26788.7</v>
       </c>
       <c r="T90">
-        <v>45072.7783321454</v>
+        <v>45072.8</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -9677,7 +9680,7 @@
         <v>772</v>
       </c>
       <c r="E91" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F91">
         <v>324.1</v>
@@ -9722,7 +9725,7 @@
         <v>24986.5</v>
       </c>
       <c r="T91">
-        <v>37855.84811529934</v>
+        <v>37855.8</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -9739,7 +9742,7 @@
         <v>773</v>
       </c>
       <c r="E92" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F92">
         <v>409.8</v>
@@ -9784,7 +9787,7 @@
         <v>393768</v>
       </c>
       <c r="T92">
-        <v>741666.4740259739</v>
+        <v>741666.5</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -9801,7 +9804,7 @@
         <v>774</v>
       </c>
       <c r="E93" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F93">
         <v>4170.2</v>
@@ -9846,7 +9849,7 @@
         <v>15077.6</v>
       </c>
       <c r="T93">
-        <v>39242.22278481012</v>
+        <v>39242.2</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -9863,7 +9866,7 @@
         <v>775</v>
       </c>
       <c r="E94" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F94">
         <v>134.6</v>
@@ -9908,7 +9911,7 @@
         <v>5410.5</v>
       </c>
       <c r="T94">
-        <v>3753.285381750466</v>
+        <v>3753.3</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -9925,7 +9928,7 @@
         <v>776</v>
       </c>
       <c r="E95" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F95">
         <v>290</v>
@@ -9970,7 +9973,7 @@
         <v>6339.5</v>
       </c>
       <c r="T95">
-        <v>17500.209048372</v>
+        <v>17500.2</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -9987,7 +9990,7 @@
         <v>777</v>
       </c>
       <c r="E96" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F96">
         <v>705.9</v>
@@ -10032,7 +10035,7 @@
         <v>9713.4</v>
       </c>
       <c r="T96">
-        <v>34993.34742516668</v>
+        <v>34993.3</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -10049,7 +10052,7 @@
         <v>778</v>
       </c>
       <c r="E97" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F97">
         <v>109.2</v>
@@ -10094,7 +10097,7 @@
         <v>3491.2</v>
       </c>
       <c r="T97">
-        <v>8126.638973246566</v>
+        <v>8126.6</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -10111,7 +10114,7 @@
         <v>779</v>
       </c>
       <c r="E98" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F98">
         <v>252.4</v>
@@ -10156,7 +10159,7 @@
         <v>3194.4</v>
       </c>
       <c r="T98">
-        <v>7224.247028199566</v>
+        <v>7224.2</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -10173,7 +10176,7 @@
         <v>780</v>
       </c>
       <c r="E99" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F99">
         <v>216</v>
@@ -10218,7 +10221,7 @@
         <v>7776.6</v>
       </c>
       <c r="T99">
-        <v>13097.21128783992</v>
+        <v>13097.2</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -10235,7 +10238,7 @@
         <v>781</v>
       </c>
       <c r="E100" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F100">
         <v>137.9</v>
@@ -10280,7 +10283,7 @@
         <v>2589.3</v>
       </c>
       <c r="T100">
-        <v>7805.433239436619</v>
+        <v>7805.4</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -10297,7 +10300,7 @@
         <v>782</v>
       </c>
       <c r="E101" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F101">
         <v>165.3</v>
@@ -10342,7 +10345,7 @@
         <v>7177.3</v>
       </c>
       <c r="T101">
-        <v>30492.99516196887</v>
+        <v>30493</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -10359,7 +10362,7 @@
         <v>783</v>
       </c>
       <c r="E102" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F102">
         <v>161.4</v>
@@ -10404,7 +10407,7 @@
         <v>8191.5</v>
       </c>
       <c r="T102">
-        <v>14509.33129032258</v>
+        <v>14509.3</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -10421,7 +10424,7 @@
         <v>784</v>
       </c>
       <c r="E103" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F103">
         <v>159.3</v>
@@ -10466,7 +10469,7 @@
         <v>3473.9</v>
       </c>
       <c r="T103">
-        <v>8098.153767560663</v>
+        <v>8098.2</v>
       </c>
     </row>
     <row r="104" spans="1:20">
@@ -10483,7 +10486,7 @@
         <v>785</v>
       </c>
       <c r="E104" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F104">
         <v>223.1</v>
@@ -10528,7 +10531,7 @@
         <v>3795.5</v>
       </c>
       <c r="T104">
-        <v>9633.111972207373</v>
+        <v>9633.1</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -10545,7 +10548,7 @@
         <v>786</v>
       </c>
       <c r="E105" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F105">
         <v>146.2</v>
@@ -10590,7 +10593,7 @@
         <v>6385.9</v>
       </c>
       <c r="T105">
-        <v>9189.974712114235</v>
+        <v>9190</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -10607,7 +10610,7 @@
         <v>787</v>
       </c>
       <c r="E106" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F106">
         <v>229.5</v>
@@ -10652,7 +10655,7 @@
         <v>7718.6</v>
       </c>
       <c r="T106">
-        <v>14664.0501559792</v>
+        <v>14664.1</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -10669,7 +10672,7 @@
         <v>788</v>
       </c>
       <c r="E107" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F107">
         <v>232.2</v>
@@ -10714,7 +10717,7 @@
         <v>3086.3</v>
       </c>
       <c r="T107">
-        <v>8603.509686847599</v>
+        <v>8603.5</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -10731,7 +10734,7 @@
         <v>789</v>
       </c>
       <c r="E108" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F108">
         <v>344</v>
@@ -10776,7 +10779,7 @@
         <v>6176.9</v>
       </c>
       <c r="T108">
-        <v>6806.397846175551</v>
+        <v>6806.4</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -10793,7 +10796,7 @@
         <v>790</v>
       </c>
       <c r="E109" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F109">
         <v>753.5</v>
@@ -10838,7 +10841,7 @@
         <v>10770.6</v>
       </c>
       <c r="T109">
-        <v>15796.98052497883</v>
+        <v>15797</v>
       </c>
     </row>
     <row r="110" spans="1:20">
@@ -10855,7 +10858,7 @@
         <v>791</v>
       </c>
       <c r="E110" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F110">
         <v>56</v>
@@ -10900,7 +10903,7 @@
         <v>3104.4</v>
       </c>
       <c r="T110">
-        <v>6330.622641509434</v>
+        <v>6330.6</v>
       </c>
     </row>
     <row r="111" spans="1:20">
@@ -10917,7 +10920,7 @@
         <v>792</v>
       </c>
       <c r="E111" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F111">
         <v>195.7</v>
@@ -10962,7 +10965,7 @@
         <v>3208.2</v>
       </c>
       <c r="T111">
-        <v>4647.921232876713</v>
+        <v>4647.9</v>
       </c>
     </row>
     <row r="112" spans="1:20">
@@ -10979,7 +10982,7 @@
         <v>793</v>
       </c>
       <c r="E112" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F112">
         <v>132.5</v>
@@ -11024,7 +11027,7 @@
         <v>3657.4</v>
       </c>
       <c r="T112">
-        <v>4945.778375733856</v>
+        <v>4945.8</v>
       </c>
     </row>
     <row r="113" spans="1:20">
@@ -11041,7 +11044,7 @@
         <v>794</v>
       </c>
       <c r="E113" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F113">
         <v>172.5</v>
@@ -11086,7 +11089,7 @@
         <v>4772.8</v>
       </c>
       <c r="T113">
-        <v>7827.132950990615</v>
+        <v>7827.1</v>
       </c>
     </row>
     <row r="114" spans="1:20">
@@ -11103,7 +11106,7 @@
         <v>795</v>
       </c>
       <c r="E114" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F114">
         <v>108.5</v>
@@ -11148,7 +11151,7 @@
         <v>1743</v>
       </c>
       <c r="T114">
-        <v>2238.390182730204</v>
+        <v>2238.4</v>
       </c>
     </row>
     <row r="115" spans="1:20">
@@ -11165,7 +11168,7 @@
         <v>796</v>
       </c>
       <c r="E115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F115">
         <v>105.8</v>
@@ -11210,7 +11213,7 @@
         <v>22350.6</v>
       </c>
       <c r="T115">
-        <v>4990.048854447439</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="116" spans="1:20">
@@ -11227,7 +11230,7 @@
         <v>797</v>
       </c>
       <c r="E116" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F116">
         <v>1642.3</v>
@@ -11272,7 +11275,7 @@
         <v>4488.2</v>
       </c>
       <c r="T116">
-        <v>6975.709294199861</v>
+        <v>6975.7</v>
       </c>
     </row>
     <row r="117" spans="1:20">
@@ -11289,7 +11292,7 @@
         <v>798</v>
       </c>
       <c r="E117" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F117">
         <v>154.1</v>
@@ -11334,7 +11337,7 @@
         <v>2229.5</v>
       </c>
       <c r="T117">
-        <v>3243.455337690632</v>
+        <v>3243.5</v>
       </c>
     </row>
     <row r="118" spans="1:20">
@@ -11351,7 +11354,7 @@
         <v>799</v>
       </c>
       <c r="E118" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F118">
         <v>161.7</v>
@@ -11396,7 +11399,7 @@
         <v>2293.2</v>
       </c>
       <c r="T118">
-        <v>5867.631236442517</v>
+        <v>5867.6</v>
       </c>
     </row>
     <row r="119" spans="1:20">
@@ -11413,7 +11416,7 @@
         <v>800</v>
       </c>
       <c r="E119" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F119">
         <v>61.5</v>
@@ -11458,7 +11461,7 @@
         <v>5151.2</v>
       </c>
       <c r="T119">
-        <v>5651.975754449318</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="120" spans="1:20">
@@ -11475,7 +11478,7 @@
         <v>801</v>
       </c>
       <c r="E120" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F120">
         <v>270</v>
@@ -11520,7 +11523,7 @@
         <v>2819.4</v>
       </c>
       <c r="T120">
-        <v>4119.218383311604</v>
+        <v>4119.2</v>
       </c>
     </row>
     <row r="121" spans="1:20">
@@ -11537,7 +11540,7 @@
         <v>802</v>
       </c>
       <c r="E121" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F121">
         <v>81.3</v>
@@ -11582,7 +11585,7 @@
         <v>10528.6</v>
       </c>
       <c r="T121">
-        <v>8058.253536452666</v>
+        <v>8058.3</v>
       </c>
     </row>
     <row r="122" spans="1:20">
@@ -11599,7 +11602,7 @@
         <v>803</v>
       </c>
       <c r="E122" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F122">
         <v>313.7</v>
@@ -11644,7 +11647,7 @@
         <v>6596.5</v>
       </c>
       <c r="T122">
-        <v>17285.81729598052</v>
+        <v>17285.8</v>
       </c>
     </row>
     <row r="123" spans="1:20">
@@ -11661,7 +11664,7 @@
         <v>804</v>
       </c>
       <c r="E123" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F123">
         <v>210.9</v>
@@ -11706,7 +11709,7 @@
         <v>2158.1</v>
       </c>
       <c r="T123">
-        <v>2205.951051422513</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="124" spans="1:20">
@@ -11723,7 +11726,7 @@
         <v>805</v>
       </c>
       <c r="E124" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F124">
         <v>159.4</v>
@@ -11768,7 +11771,7 @@
         <v>3700.8</v>
       </c>
       <c r="T124">
-        <v>4852.617344658024</v>
+        <v>4852.6</v>
       </c>
     </row>
     <row r="125" spans="1:20">
@@ -11785,7 +11788,7 @@
         <v>806</v>
       </c>
       <c r="E125" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F125">
         <v>312.7</v>
@@ -11830,7 +11833,7 @@
         <v>6442.3</v>
       </c>
       <c r="T125">
-        <v>5699.549582660667</v>
+        <v>5699.5</v>
       </c>
     </row>
     <row r="126" spans="1:20">
@@ -11847,7 +11850,7 @@
         <v>807</v>
       </c>
       <c r="E126" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F126">
         <v>355</v>
@@ -11892,7 +11895,7 @@
         <v>12189.9</v>
       </c>
       <c r="T126">
-        <v>7962.19119804401</v>
+        <v>7962.2</v>
       </c>
     </row>
     <row r="127" spans="1:20">
@@ -11909,7 +11912,7 @@
         <v>808</v>
       </c>
       <c r="E127" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F127">
         <v>229.5</v>
@@ -11954,7 +11957,7 @@
         <v>1872.9</v>
       </c>
       <c r="T127">
-        <v>3624.720512820513</v>
+        <v>3624.7</v>
       </c>
     </row>
     <row r="128" spans="1:20">
@@ -11971,7 +11974,7 @@
         <v>809</v>
       </c>
       <c r="E128" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F128">
         <v>178.9</v>
@@ -12016,7 +12019,7 @@
         <v>3408</v>
       </c>
       <c r="T128">
-        <v>3729.972489683631</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="129" spans="1:20">
@@ -12033,7 +12036,7 @@
         <v>810</v>
       </c>
       <c r="E129" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -12078,7 +12081,7 @@
         <v>3613.6</v>
       </c>
       <c r="T129">
-        <v>3429.793103448276</v>
+        <v>3429.8</v>
       </c>
     </row>
     <row r="130" spans="1:20">
@@ -12095,7 +12098,7 @@
         <v>811</v>
       </c>
       <c r="E130" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F130">
         <v>990</v>
@@ -12140,7 +12143,7 @@
         <v>28160.2</v>
       </c>
       <c r="T130">
-        <v>44079.10969793323</v>
+        <v>44079.1</v>
       </c>
     </row>
     <row r="131" spans="1:20">
@@ -12157,7 +12160,7 @@
         <v>812</v>
       </c>
       <c r="E131" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F131">
         <v>179.1</v>
@@ -12202,7 +12205,7 @@
         <v>3511.5</v>
       </c>
       <c r="T131">
-        <v>3181.984536082474</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="132" spans="1:20">
@@ -12219,7 +12222,7 @@
         <v>813</v>
       </c>
       <c r="E132" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F132">
         <v>116.4</v>
@@ -12264,7 +12267,7 @@
         <v>2776.4</v>
       </c>
       <c r="T132">
-        <v>2337.26240300964</v>
+        <v>2337.3</v>
       </c>
     </row>
     <row r="133" spans="1:20">
@@ -12281,7 +12284,7 @@
         <v>814</v>
       </c>
       <c r="E133" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F133">
         <v>267.1</v>
@@ -12326,7 +12329,7 @@
         <v>4789.6</v>
       </c>
       <c r="T133">
-        <v>3121.38184079602</v>
+        <v>3121.4</v>
       </c>
     </row>
     <row r="134" spans="1:20">
@@ -12343,7 +12346,7 @@
         <v>815</v>
       </c>
       <c r="E134" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F134">
         <v>235.6</v>
@@ -12388,7 +12391,7 @@
         <v>2211.2</v>
       </c>
       <c r="T134">
-        <v>2019.811291569992</v>
+        <v>2019.8</v>
       </c>
     </row>
     <row r="135" spans="1:20">
@@ -12405,7 +12408,7 @@
         <v>816</v>
       </c>
       <c r="E135" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F135">
         <v>168.1</v>
@@ -12450,7 +12453,7 @@
         <v>3320</v>
       </c>
       <c r="T135">
-        <v>2363.215139442231</v>
+        <v>2363.2</v>
       </c>
     </row>
     <row r="136" spans="1:20">
@@ -12467,7 +12470,7 @@
         <v>817</v>
       </c>
       <c r="E136" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F136">
         <v>611</v>
@@ -12512,7 +12515,7 @@
         <v>7136.8</v>
       </c>
       <c r="T136">
-        <v>5432.381344902386</v>
+        <v>5432.4</v>
       </c>
     </row>
     <row r="137" spans="1:20">
@@ -12529,7 +12532,7 @@
         <v>818</v>
       </c>
       <c r="E137" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F137">
         <v>371.8</v>
@@ -12574,7 +12577,7 @@
         <v>8351.299999999999</v>
       </c>
       <c r="T137">
-        <v>18690.32130384168</v>
+        <v>18690.3</v>
       </c>
     </row>
     <row r="138" spans="1:20">
@@ -12591,7 +12594,7 @@
         <v>819</v>
       </c>
       <c r="E138" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F138">
         <v>146.2</v>
@@ -12636,7 +12639,7 @@
         <v>1557.9</v>
       </c>
       <c r="T138">
-        <v>1552.53287743293</v>
+        <v>1552.5</v>
       </c>
     </row>
     <row r="139" spans="1:20">
@@ -12653,7 +12656,7 @@
         <v>820</v>
       </c>
       <c r="E139" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F139">
         <v>160.5</v>
@@ -12698,7 +12701,7 @@
         <v>21877.5</v>
       </c>
       <c r="T139">
-        <v>4297.885808270677</v>
+        <v>4297.9</v>
       </c>
     </row>
     <row r="140" spans="1:20">
@@ -12715,7 +12718,7 @@
         <v>821</v>
       </c>
       <c r="E140" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F140">
         <v>130.6</v>
@@ -12760,7 +12763,7 @@
         <v>1537.6</v>
       </c>
       <c r="T140">
-        <v>3262.833621434745</v>
+        <v>3262.8</v>
       </c>
     </row>
     <row r="141" spans="1:20">
@@ -12777,7 +12780,7 @@
         <v>822</v>
       </c>
       <c r="E141" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F141">
         <v>564.3</v>
@@ -12822,7 +12825,7 @@
         <v>17532.1</v>
       </c>
       <c r="T141">
-        <v>12365.88052905464</v>
+        <v>12365.9</v>
       </c>
     </row>
     <row r="142" spans="1:20">
@@ -12839,7 +12842,7 @@
         <v>823</v>
       </c>
       <c r="E142" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F142">
         <v>751.9</v>
@@ -12884,7 +12887,7 @@
         <v>13046.4</v>
       </c>
       <c r="T142">
-        <v>13848.80635551142</v>
+        <v>13848.8</v>
       </c>
     </row>
     <row r="143" spans="1:20">
@@ -12901,7 +12904,7 @@
         <v>824</v>
       </c>
       <c r="E143" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F143">
         <v>3581.6</v>
@@ -12946,7 +12949,7 @@
         <v>101401.1</v>
       </c>
       <c r="T143">
-        <v>177691.6340206186</v>
+        <v>177691.6</v>
       </c>
     </row>
     <row r="144" spans="1:20">
@@ -12963,7 +12966,7 @@
         <v>825</v>
       </c>
       <c r="E144" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F144">
         <v>1042.6</v>
@@ -13008,7 +13011,7 @@
         <v>15656.5</v>
       </c>
       <c r="T144">
-        <v>17905.12577319588</v>
+        <v>17905.1</v>
       </c>
     </row>
     <row r="145" spans="1:20">
@@ -13025,7 +13028,7 @@
         <v>826</v>
       </c>
       <c r="E145" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F145">
         <v>210.8</v>
@@ -13070,7 +13073,7 @@
         <v>9438.700000000001</v>
       </c>
       <c r="T145">
-        <v>7922.350533807828</v>
+        <v>7922.4</v>
       </c>
     </row>
     <row r="146" spans="1:20">
@@ -13087,7 +13090,7 @@
         <v>827</v>
       </c>
       <c r="E146" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F146">
         <v>212.2</v>
@@ -13132,7 +13135,7 @@
         <v>47950</v>
       </c>
       <c r="T146">
-        <v>12141.30741797432</v>
+        <v>12141.3</v>
       </c>
     </row>
     <row r="147" spans="1:20">
@@ -13149,7 +13152,7 @@
         <v>828</v>
       </c>
       <c r="E147" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F147">
         <v>336.2</v>
@@ -13194,7 +13197,7 @@
         <v>3614.8</v>
       </c>
       <c r="T147">
-        <v>5731.629051620648</v>
+        <v>5731.6</v>
       </c>
     </row>
     <row r="148" spans="1:20">
@@ -13211,7 +13214,7 @@
         <v>829</v>
       </c>
       <c r="E148" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F148">
         <v>323.6</v>
@@ -13256,7 +13259,7 @@
         <v>3895</v>
       </c>
       <c r="T148">
-        <v>3383.836861768369</v>
+        <v>3383.8</v>
       </c>
     </row>
     <row r="149" spans="1:20">
@@ -13273,7 +13276,7 @@
         <v>830</v>
       </c>
       <c r="E149" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F149">
         <v>1016</v>
@@ -13318,7 +13321,7 @@
         <v>10971.9</v>
       </c>
       <c r="T149">
-        <v>10939.023977433</v>
+        <v>10939</v>
       </c>
     </row>
     <row r="150" spans="1:20">
@@ -13335,7 +13338,7 @@
         <v>831</v>
       </c>
       <c r="E150" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F150">
         <v>228.8</v>
@@ -13380,7 +13383,7 @@
         <v>8001.6</v>
       </c>
       <c r="T150">
-        <v>4846.987714987715</v>
+        <v>4847</v>
       </c>
     </row>
     <row r="151" spans="1:20">
@@ -13397,7 +13400,7 @@
         <v>832</v>
       </c>
       <c r="E151" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F151">
         <v>751.8</v>
@@ -13442,7 +13445,7 @@
         <v>13160.5</v>
       </c>
       <c r="T151">
-        <v>7919.120751988429</v>
+        <v>7919.1</v>
       </c>
     </row>
     <row r="152" spans="1:20">
@@ -13459,7 +13462,7 @@
         <v>833</v>
       </c>
       <c r="E152" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F152">
         <v>314.5</v>
@@ -13504,7 +13507,7 @@
         <v>9662.299999999999</v>
       </c>
       <c r="T152">
-        <v>5175.842054263566</v>
+        <v>5175.8</v>
       </c>
     </row>
     <row r="153" spans="1:20">
@@ -13521,7 +13524,7 @@
         <v>834</v>
       </c>
       <c r="E153" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F153">
         <v>618.2</v>
@@ -13566,7 +13569,7 @@
         <v>15784.2</v>
       </c>
       <c r="T153">
-        <v>23806.08541930457</v>
+        <v>23806.1</v>
       </c>
     </row>
     <row r="154" spans="1:20">
@@ -13583,7 +13586,7 @@
         <v>835</v>
       </c>
       <c r="E154" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -13628,7 +13631,7 @@
         <v>42269.8</v>
       </c>
       <c r="T154">
-        <v>48355.53251318102</v>
+        <v>48355.5</v>
       </c>
     </row>
     <row r="155" spans="1:20">
@@ -13645,7 +13648,7 @@
         <v>836</v>
       </c>
       <c r="E155" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F155">
         <v>40.3</v>
@@ -13690,7 +13693,7 @@
         <v>104089.8</v>
       </c>
       <c r="T155">
-        <v>167330.647496617</v>
+        <v>167330.6</v>
       </c>
     </row>
     <row r="156" spans="1:20">
@@ -13707,7 +13710,7 @@
         <v>837</v>
       </c>
       <c r="E156" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F156">
         <v>102.8</v>
@@ -13752,7 +13755,7 @@
         <v>9027.6</v>
       </c>
       <c r="T156">
-        <v>23919.87391304348</v>
+        <v>23919.9</v>
       </c>
     </row>
     <row r="157" spans="1:20">
@@ -13769,7 +13772,7 @@
         <v>838</v>
       </c>
       <c r="E157" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F157">
         <v>60.4</v>
@@ -13814,7 +13817,7 @@
         <v>35074</v>
       </c>
       <c r="T157">
-        <v>28407.97433460076</v>
+        <v>28408</v>
       </c>
     </row>
     <row r="158" spans="1:20">
@@ -13831,7 +13834,7 @@
         <v>839</v>
       </c>
       <c r="E158" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F158">
         <v>144.2</v>
@@ -13876,7 +13879,7 @@
         <v>12798.6</v>
       </c>
       <c r="T158">
-        <v>18751.74569460391</v>
+        <v>18751.7</v>
       </c>
     </row>
     <row r="159" spans="1:20">
@@ -13893,7 +13896,7 @@
         <v>840</v>
       </c>
       <c r="E159" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -13938,7 +13941,7 @@
         <v>38855.8</v>
       </c>
       <c r="T159">
-        <v>27280.27817745803</v>
+        <v>27280.3</v>
       </c>
     </row>
     <row r="160" spans="1:20">
@@ -13955,7 +13958,7 @@
         <v>841</v>
       </c>
       <c r="E160" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -14000,7 +14003,7 @@
         <v>4481.5</v>
       </c>
       <c r="T160">
-        <v>8702.678240740741</v>
+        <v>8702.700000000001</v>
       </c>
     </row>
     <row r="161" spans="1:20">
@@ -14017,7 +14020,7 @@
         <v>842</v>
       </c>
       <c r="E161" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F161">
         <v>415.8</v>
@@ -14062,7 +14065,7 @@
         <v>1521.1</v>
       </c>
       <c r="T161">
-        <v>11780.46419098143</v>
+        <v>11780.5</v>
       </c>
     </row>
     <row r="162" spans="1:20">
@@ -14079,7 +14082,7 @@
         <v>843</v>
       </c>
       <c r="E162" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F162">
         <v>207.5</v>
@@ -14124,7 +14127,7 @@
         <v>24312.5</v>
       </c>
       <c r="T162">
-        <v>26957.28991971455</v>
+        <v>26957.3</v>
       </c>
     </row>
     <row r="163" spans="1:20">
@@ -14141,7 +14144,7 @@
         <v>844</v>
       </c>
       <c r="E163" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F163">
         <v>590.5</v>
@@ -14186,7 +14189,7 @@
         <v>2823.3</v>
       </c>
       <c r="T163">
-        <v>4077.535329341318</v>
+        <v>4077.5</v>
       </c>
     </row>
     <row r="164" spans="1:20">
@@ -14203,7 +14206,7 @@
         <v>845</v>
       </c>
       <c r="E164" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F164">
         <v>231.4</v>
@@ -14248,7 +14251,7 @@
         <v>13263.9</v>
       </c>
       <c r="T164">
-        <v>18543.80552423901</v>
+        <v>18543.8</v>
       </c>
     </row>
     <row r="165" spans="1:20">
@@ -14265,7 +14268,7 @@
         <v>846</v>
       </c>
       <c r="E165" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F165">
         <v>457.1</v>
@@ -14310,7 +14313,7 @@
         <v>3414.9</v>
       </c>
       <c r="T165">
-        <v>5141.377121771217</v>
+        <v>5141.4</v>
       </c>
     </row>
     <row r="166" spans="1:20">
@@ -14327,7 +14330,7 @@
         <v>847</v>
       </c>
       <c r="E166" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F166">
         <v>408.5</v>
@@ -14372,7 +14375,7 @@
         <v>15966.3</v>
       </c>
       <c r="T166">
-        <v>15334.27397260274</v>
+        <v>15334.3</v>
       </c>
     </row>
     <row r="167" spans="1:20">
@@ -14389,7 +14392,7 @@
         <v>848</v>
       </c>
       <c r="E167" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F167">
         <v>112.3</v>
@@ -14434,7 +14437,7 @@
         <v>11660.3</v>
       </c>
       <c r="T167">
-        <v>15156.60611303345</v>
+        <v>15156.6</v>
       </c>
     </row>
     <row r="168" spans="1:20">
@@ -14451,7 +14454,7 @@
         <v>849</v>
       </c>
       <c r="E168" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F168">
         <v>360.1</v>
@@ -14496,7 +14499,7 @@
         <v>19619</v>
       </c>
       <c r="T168">
-        <v>40609.36823361823</v>
+        <v>40609.4</v>
       </c>
     </row>
     <row r="169" spans="1:20">
@@ -14513,7 +14516,7 @@
         <v>850</v>
       </c>
       <c r="E169" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F169">
         <v>126.2</v>
@@ -14558,7 +14561,7 @@
         <v>18202.1</v>
       </c>
       <c r="T169">
-        <v>23295.85084745763</v>
+        <v>23295.9</v>
       </c>
     </row>
     <row r="170" spans="1:20">
@@ -14575,7 +14578,7 @@
         <v>851</v>
       </c>
       <c r="E170" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F170">
         <v>394.3</v>
@@ -14620,7 +14623,7 @@
         <v>3203.5</v>
       </c>
       <c r="T170">
-        <v>2411.64908384231</v>
+        <v>2411.6</v>
       </c>
     </row>
     <row r="171" spans="1:20">
@@ -14637,7 +14640,7 @@
         <v>852</v>
       </c>
       <c r="E171" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F171">
         <v>517</v>
@@ -14682,7 +14685,7 @@
         <v>4021.4</v>
       </c>
       <c r="T171">
-        <v>11202.7392578125</v>
+        <v>11202.7</v>
       </c>
     </row>
     <row r="172" spans="1:20">
@@ -14699,7 +14702,7 @@
         <v>853</v>
       </c>
       <c r="E172" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F172">
         <v>568.4</v>
@@ -14744,7 +14747,7 @@
         <v>10110.5</v>
       </c>
       <c r="T172">
-        <v>12270.86806056236</v>
+        <v>12270.9</v>
       </c>
     </row>
     <row r="173" spans="1:20">
@@ -14761,7 +14764,7 @@
         <v>854</v>
       </c>
       <c r="E173" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F173">
         <v>426.3</v>
@@ -14806,7 +14809,7 @@
         <v>3391</v>
       </c>
       <c r="T173">
-        <v>12160.99659400545</v>
+        <v>12161</v>
       </c>
     </row>
     <row r="174" spans="1:20">
@@ -14823,7 +14826,7 @@
         <v>855</v>
       </c>
       <c r="E174" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F174">
         <v>225.9</v>
@@ -14868,7 +14871,7 @@
         <v>7672.2</v>
       </c>
       <c r="T174">
-        <v>15330.25705794948</v>
+        <v>15330.3</v>
       </c>
     </row>
     <row r="175" spans="1:20">
@@ -14885,7 +14888,7 @@
         <v>856</v>
       </c>
       <c r="E175" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -14930,7 +14933,7 @@
         <v>4531.6</v>
       </c>
       <c r="T175">
-        <v>9273.899155489318</v>
+        <v>9273.9</v>
       </c>
     </row>
     <row r="176" spans="1:20">
@@ -14947,7 +14950,7 @@
         <v>857</v>
       </c>
       <c r="E176" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F176">
         <v>300.1</v>
@@ -14992,7 +14995,7 @@
         <v>4965.3</v>
       </c>
       <c r="T176">
-        <v>5250.347298384148</v>
+        <v>5250.3</v>
       </c>
     </row>
     <row r="177" spans="1:20">
@@ -15009,7 +15012,7 @@
         <v>858</v>
       </c>
       <c r="E177" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F177">
         <v>1056.1</v>
@@ -15054,7 +15057,7 @@
         <v>15642.3</v>
       </c>
       <c r="T177">
-        <v>15943.40203014457</v>
+        <v>15943.4</v>
       </c>
     </row>
     <row r="178" spans="1:20">
@@ -15071,7 +15074,7 @@
         <v>859</v>
       </c>
       <c r="E178" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F178">
         <v>660.5</v>
@@ -15116,7 +15119,7 @@
         <v>5194.3</v>
       </c>
       <c r="T178">
-        <v>6285.255380661741</v>
+        <v>6285.3</v>
       </c>
     </row>
     <row r="179" spans="1:20">
@@ -15133,7 +15136,7 @@
         <v>860</v>
       </c>
       <c r="E179" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F179">
         <v>308</v>
@@ -15178,7 +15181,7 @@
         <v>5867.1</v>
       </c>
       <c r="T179">
-        <v>11021.52641878669</v>
+        <v>11021.5</v>
       </c>
     </row>
     <row r="180" spans="1:20">
@@ -15195,7 +15198,7 @@
         <v>861</v>
       </c>
       <c r="E180" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F180">
         <v>198.5</v>
@@ -15240,7 +15243,7 @@
         <v>3204.7</v>
       </c>
       <c r="T180">
-        <v>2636.683613609699</v>
+        <v>2636.7</v>
       </c>
     </row>
     <row r="181" spans="1:20">
@@ -15257,7 +15260,7 @@
         <v>862</v>
       </c>
       <c r="E181" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F181">
         <v>181.7</v>
@@ -15302,7 +15305,7 @@
         <v>3922.2</v>
       </c>
       <c r="T181">
-        <v>3433.029908972692</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="182" spans="1:20">
@@ -15319,7 +15322,7 @@
         <v>863</v>
       </c>
       <c r="E182" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F182">
         <v>355.9</v>
@@ -15364,7 +15367,7 @@
         <v>5816.5</v>
       </c>
       <c r="T182">
-        <v>3663.028001898434</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="183" spans="1:20">
@@ -15381,7 +15384,7 @@
         <v>864</v>
       </c>
       <c r="E183" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F183">
         <v>139.7</v>
@@ -15426,7 +15429,7 @@
         <v>1930</v>
       </c>
       <c r="T183">
-        <v>2199.490662139219</v>
+        <v>2199.5</v>
       </c>
     </row>
     <row r="184" spans="1:20">
@@ -15443,7 +15446,7 @@
         <v>865</v>
       </c>
       <c r="E184" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F184">
         <v>102.2</v>
@@ -15505,7 +15508,7 @@
         <v>866</v>
       </c>
       <c r="E185" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F185">
         <v>201.6</v>
@@ -15550,7 +15553,7 @@
         <v>2687.7</v>
       </c>
       <c r="T185">
-        <v>1837.959183673469</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="186" spans="1:20">
@@ -15567,7 +15570,7 @@
         <v>867</v>
       </c>
       <c r="E186" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F186">
         <v>84.7</v>
@@ -15612,7 +15615,7 @@
         <v>1955.1</v>
       </c>
       <c r="T186">
-        <v>1493.170381020848</v>
+        <v>1493.2</v>
       </c>
     </row>
     <row r="187" spans="1:20">
@@ -15629,7 +15632,7 @@
         <v>868</v>
       </c>
       <c r="E187" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F187">
         <v>120.1</v>
@@ -15674,7 +15677,7 @@
         <v>8526.5</v>
       </c>
       <c r="T187">
-        <v>7748.566748566749</v>
+        <v>7748.6</v>
       </c>
     </row>
     <row r="188" spans="1:20">
@@ -15691,7 +15694,7 @@
         <v>869</v>
       </c>
       <c r="E188" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F188">
         <v>175.5</v>
@@ -15736,7 +15739,7 @@
         <v>3520.7</v>
       </c>
       <c r="T188">
-        <v>1706.526700136924</v>
+        <v>1706.5</v>
       </c>
     </row>
     <row r="189" spans="1:20">
@@ -15753,7 +15756,7 @@
         <v>870</v>
       </c>
       <c r="E189" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F189">
         <v>181.8</v>
@@ -15798,7 +15801,7 @@
         <v>2016.3</v>
       </c>
       <c r="T189">
-        <v>3430.588235294118</v>
+        <v>3430.6</v>
       </c>
     </row>
     <row r="190" spans="1:20">
@@ -15815,7 +15818,7 @@
         <v>871</v>
       </c>
       <c r="E190" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F190">
         <v>254.8</v>
@@ -15860,7 +15863,7 @@
         <v>5662.7</v>
       </c>
       <c r="T190">
-        <v>4769.23076923077</v>
+        <v>4769.2</v>
       </c>
     </row>
     <row r="191" spans="1:20">
@@ -15877,7 +15880,7 @@
         <v>872</v>
       </c>
       <c r="E191" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F191">
         <v>132.2</v>
@@ -15939,7 +15942,7 @@
         <v>873</v>
       </c>
       <c r="E192" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F192">
         <v>119.3</v>
@@ -15984,7 +15987,7 @@
         <v>4895.3</v>
       </c>
       <c r="T192">
-        <v>6947.25078229772</v>
+        <v>6947.3</v>
       </c>
     </row>
     <row r="193" spans="1:20">
@@ -16001,7 +16004,7 @@
         <v>874</v>
       </c>
       <c r="E193" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F193">
         <v>186.2</v>
@@ -16046,7 +16049,7 @@
         <v>4165.6</v>
       </c>
       <c r="T193">
-        <v>4646.007816862088</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="194" spans="1:20">
@@ -16063,7 +16066,7 @@
         <v>875</v>
       </c>
       <c r="E194" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F194">
         <v>98.40000000000001</v>
@@ -16108,7 +16111,7 @@
         <v>2204.8</v>
       </c>
       <c r="T194">
-        <v>3348.130841121495</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="195" spans="1:20">
@@ -16125,7 +16128,7 @@
         <v>876</v>
       </c>
       <c r="E195" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F195">
         <v>935.5</v>
@@ -16170,7 +16173,7 @@
         <v>6061.7</v>
       </c>
       <c r="T195">
-        <v>3147.933884297521</v>
+        <v>3147.9</v>
       </c>
     </row>
     <row r="196" spans="1:20">
@@ -16187,7 +16190,7 @@
         <v>877</v>
       </c>
       <c r="E196" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F196">
         <v>264.6</v>
@@ -16232,7 +16235,7 @@
         <v>5901.5</v>
       </c>
       <c r="T196">
-        <v>7757.735004965244</v>
+        <v>7757.7</v>
       </c>
     </row>
     <row r="197" spans="1:20">
@@ -16249,7 +16252,7 @@
         <v>878</v>
       </c>
       <c r="E197" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F197">
         <v>400.7</v>
@@ -16294,7 +16297,7 @@
         <v>17940.6</v>
       </c>
       <c r="T197">
-        <v>23900.05829015544</v>
+        <v>23900.1</v>
       </c>
     </row>
     <row r="198" spans="1:20">
@@ -16311,7 +16314,7 @@
         <v>879</v>
       </c>
       <c r="E198" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -16356,7 +16359,7 @@
         <v>3236.6</v>
       </c>
       <c r="T198">
-        <v>11438.00804020101</v>
+        <v>11438</v>
       </c>
     </row>
     <row r="199" spans="1:20">
@@ -16373,7 +16376,7 @@
         <v>880</v>
       </c>
       <c r="E199" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F199">
         <v>244</v>
@@ -16418,7 +16421,7 @@
         <v>3051.3</v>
       </c>
       <c r="T199">
-        <v>3363.545556805399</v>
+        <v>3363.5</v>
       </c>
     </row>
     <row r="200" spans="1:20">
@@ -16435,7 +16438,7 @@
         <v>881</v>
       </c>
       <c r="E200" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F200">
         <v>176.1</v>
@@ -16480,7 +16483,7 @@
         <v>2144</v>
       </c>
       <c r="T200">
-        <v>5487.386750788643</v>
+        <v>5487.4</v>
       </c>
     </row>
     <row r="201" spans="1:20">
@@ -16497,7 +16500,7 @@
         <v>882</v>
       </c>
       <c r="E201" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F201">
         <v>140.2</v>
@@ -16542,7 +16545,7 @@
         <v>9290.5</v>
       </c>
       <c r="T201">
-        <v>10348.60065288357</v>
+        <v>10348.6</v>
       </c>
     </row>
     <row r="202" spans="1:20">
@@ -16559,7 +16562,7 @@
         <v>883</v>
       </c>
       <c r="E202" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F202">
         <v>218.7</v>
@@ -16604,7 +16607,7 @@
         <v>8176.6</v>
       </c>
       <c r="T202">
-        <v>9789.879573876795</v>
+        <v>9789.9</v>
       </c>
     </row>
     <row r="203" spans="1:20">
@@ -16621,7 +16624,7 @@
         <v>884</v>
       </c>
       <c r="E203" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F203">
         <v>136.7</v>
@@ -16666,7 +16669,7 @@
         <v>3440.6</v>
       </c>
       <c r="T203">
-        <v>4428.836538461538</v>
+        <v>4428.8</v>
       </c>
     </row>
     <row r="204" spans="1:20">
@@ -16683,7 +16686,7 @@
         <v>885</v>
       </c>
       <c r="E204" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -16728,7 +16731,7 @@
         <v>2568.4</v>
       </c>
       <c r="T204">
-        <v>11392.96833333333</v>
+        <v>11393</v>
       </c>
     </row>
     <row r="205" spans="1:20">
@@ -16745,7 +16748,7 @@
         <v>886</v>
       </c>
       <c r="E205" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F205">
         <v>167.6</v>
@@ -16790,7 +16793,7 @@
         <v>11166.2</v>
       </c>
       <c r="T205">
-        <v>3835.479020979021</v>
+        <v>3835.5</v>
       </c>
     </row>
     <row r="206" spans="1:20">
@@ -16807,7 +16810,7 @@
         <v>887</v>
       </c>
       <c r="E206" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F206">
         <v>124</v>
@@ -16852,7 +16855,7 @@
         <v>4146.5</v>
       </c>
       <c r="T206">
-        <v>7257.170607028754</v>
+        <v>7257.2</v>
       </c>
     </row>
     <row r="207" spans="1:20">
@@ -16869,7 +16872,7 @@
         <v>888</v>
       </c>
       <c r="E207" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F207">
         <v>210.7</v>
@@ -16914,7 +16917,7 @@
         <v>3700.8</v>
       </c>
       <c r="T207">
-        <v>2724.635714285714</v>
+        <v>2724.6</v>
       </c>
     </row>
     <row r="208" spans="1:20">
@@ -16931,7 +16934,7 @@
         <v>889</v>
       </c>
       <c r="E208" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F208">
         <v>193</v>
@@ -16976,7 +16979,7 @@
         <v>3812.6</v>
       </c>
       <c r="T208">
-        <v>4665.441223832529</v>
+        <v>4665.4</v>
       </c>
     </row>
     <row r="209" spans="1:20">
@@ -16993,7 +16996,7 @@
         <v>890</v>
       </c>
       <c r="E209" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F209">
         <v>232.2</v>
@@ -17038,7 +17041,7 @@
         <v>6808.5</v>
       </c>
       <c r="T209">
-        <v>7817.732832618025</v>
+        <v>7817.7</v>
       </c>
     </row>
     <row r="210" spans="1:20">
@@ -17055,7 +17058,7 @@
         <v>891</v>
       </c>
       <c r="E210" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F210">
         <v>1472.4</v>
@@ -17100,7 +17103,7 @@
         <v>23725.7</v>
       </c>
       <c r="T210">
-        <v>29785.11047191888</v>
+        <v>29785.1</v>
       </c>
     </row>
     <row r="211" spans="1:20">
@@ -17117,7 +17120,7 @@
         <v>892</v>
       </c>
       <c r="E211" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F211">
         <v>509.6</v>
@@ -17162,7 +17165,7 @@
         <v>20650.23507588533</v>
       </c>
       <c r="T211">
-        <v>12021.83194675541</v>
+        <v>12021.8</v>
       </c>
     </row>
     <row r="212" spans="1:20">
@@ -17179,7 +17182,7 @@
         <v>893</v>
       </c>
       <c r="E212" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F212">
         <v>3887.5</v>
@@ -17224,7 +17227,7 @@
         <v>34450.7624784854</v>
       </c>
       <c r="T212">
-        <v>45257.78888888889</v>
+        <v>45257.8</v>
       </c>
     </row>
     <row r="213" spans="1:20">
@@ -17241,7 +17244,7 @@
         <v>894</v>
       </c>
       <c r="E213" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F213">
         <v>2162.6</v>
@@ -17286,7 +17289,7 @@
         <v>27732.15635091496</v>
       </c>
       <c r="T213">
-        <v>44557.14946151826</v>
+        <v>44557.1</v>
       </c>
     </row>
     <row r="214" spans="1:20">
@@ -17303,7 +17306,7 @@
         <v>895</v>
       </c>
       <c r="E214" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F214">
         <v>934.1</v>
@@ -17348,7 +17351,7 @@
         <v>17952.81143031785</v>
       </c>
       <c r="T214">
-        <v>23511.8111343909</v>
+        <v>23511.8</v>
       </c>
     </row>
     <row r="215" spans="1:20">
@@ -17365,7 +17368,7 @@
         <v>896</v>
       </c>
       <c r="E215" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F215">
         <v>4921.5</v>
@@ -17410,7 +17413,7 @@
         <v>45306.98076923077</v>
       </c>
       <c r="T215">
-        <v>51193.21279373368</v>
+        <v>51193.2</v>
       </c>
     </row>
     <row r="216" spans="1:20">
@@ -17427,7 +17430,7 @@
         <v>897</v>
       </c>
       <c r="E216" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F216">
         <v>953.5</v>
@@ -17472,7 +17475,7 @@
         <v>29095.81597796143</v>
       </c>
       <c r="T216">
-        <v>42478.39319727891</v>
+        <v>42478.4</v>
       </c>
     </row>
     <row r="217" spans="1:20">
@@ -17489,7 +17492,7 @@
         <v>898</v>
       </c>
       <c r="E217" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F217">
         <v>847.3</v>
@@ -17534,7 +17537,7 @@
         <v>12660.8218663998</v>
       </c>
       <c r="T217">
-        <v>9320.962028417443</v>
+        <v>9321</v>
       </c>
     </row>
     <row r="218" spans="1:20">
@@ -17551,7 +17554,7 @@
         <v>899</v>
       </c>
       <c r="E218" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F218">
         <v>1339.4</v>
@@ -17596,7 +17599,7 @@
         <v>29091.55535390199</v>
       </c>
       <c r="T218">
-        <v>26736.70708845929</v>
+        <v>26736.7</v>
       </c>
     </row>
     <row r="219" spans="1:20">
@@ -17613,7 +17616,7 @@
         <v>900</v>
       </c>
       <c r="E219" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F219">
         <v>2737.1</v>
@@ -17658,7 +17661,7 @@
         <v>37566.30721966206</v>
       </c>
       <c r="T219">
-        <v>53465.48755490483</v>
+        <v>53465.5</v>
       </c>
     </row>
     <row r="220" spans="1:20">
@@ -17675,7 +17678,7 @@
         <v>901</v>
       </c>
       <c r="E220" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F220">
         <v>1260.8</v>
@@ -17720,7 +17723,7 @@
         <v>24906.11668928087</v>
       </c>
       <c r="T220">
-        <v>29398.10659232535</v>
+        <v>29398.1</v>
       </c>
     </row>
     <row r="221" spans="1:20">
@@ -17737,7 +17740,7 @@
         <v>902</v>
       </c>
       <c r="E221" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -17782,7 +17785,7 @@
         <v>19149.45622394282</v>
       </c>
       <c r="T221">
-        <v>23411.24242424242</v>
+        <v>23411.2</v>
       </c>
     </row>
     <row r="222" spans="1:20">
@@ -17799,7 +17802,7 @@
         <v>903</v>
       </c>
       <c r="E222" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F222">
         <v>1183.9</v>
@@ -17844,7 +17847,7 @@
         <v>15092.6592321755</v>
       </c>
       <c r="T222">
-        <v>29077.32040594419</v>
+        <v>29077.3</v>
       </c>
     </row>
   </sheetData>
@@ -17859,444 +17862,444 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D3" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="F3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B4" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D4" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="G4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D5" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E5" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F5" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G5" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H5" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B6" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D6" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E6" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F6" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G6" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H6" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B7" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C7" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E7" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G7" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H7" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B8" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C8" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D8" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E8" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F8" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G8" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H8" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C9" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D9" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E9" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F9" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G9" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H9" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B10" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C10" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D10" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E10" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F10" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G10" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H10" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B11" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C11" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D11" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E11" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G11" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H11" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B12" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C12" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D12" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E12" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F12" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G12" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H12" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B13" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C13" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D13" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E13" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="G13" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H13" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B14" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C14" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D14" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E14" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G14" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H14" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B15" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C15" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D15" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E15" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F15" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="G15" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H15" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B16" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C16" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D16" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E16" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F16" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G16" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H16" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B17" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C17" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D17" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E17" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F17" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G17" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H17" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata_raw/fixed_capital_investment_per_capita.xlsx
+++ b/data/metadata_raw/fixed_capital_investment_per_capita.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="1238">
   <si>
     <t>Code</t>
   </si>
@@ -77,6 +77,9 @@
     <t>2024</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>1700</t>
   </si>
   <si>
@@ -3599,7 +3602,7 @@
     <t>2022-08-10</t>
   </si>
   <si>
-    <t>2026-03-05</t>
+    <t>2026-08-27</t>
   </si>
   <si>
     <t>1.04.01.0006</t>
@@ -4083,10 +4086,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T222"/>
+  <dimension ref="A1:U222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4147,22 +4150,25 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F2">
         <v>583.2</v>
@@ -4209,22 +4215,25 @@
       <c r="T2">
         <v>13652.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2">
+        <v>15929.27996115059</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F3">
         <v>302.6</v>
@@ -4271,22 +4280,25 @@
       <c r="T3">
         <v>10201.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3">
+        <v>12812.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F4">
         <v>359.6</v>
@@ -4333,22 +4345,25 @@
       <c r="T4">
         <v>9889.200000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4">
+        <v>9646.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E5" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F5">
         <v>149.1</v>
@@ -4395,22 +4410,25 @@
       <c r="T5">
         <v>2791.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5">
+        <v>3980.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E6" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F6">
         <v>123.4</v>
@@ -4457,22 +4475,25 @@
       <c r="T6">
         <v>2739.8</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6">
+        <v>9035.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D7" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E7" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4519,22 +4540,25 @@
       <c r="T7">
         <v>2916.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7">
+        <v>6936.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E8" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F8">
         <v>157</v>
@@ -4581,22 +4605,25 @@
       <c r="T8">
         <v>119576</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="U8">
+        <v>49555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F9">
         <v>111.1</v>
@@ -4643,22 +4670,25 @@
       <c r="T9">
         <v>1579.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="U9">
+        <v>2882.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E10" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F10">
         <v>668.3</v>
@@ -4705,22 +4735,25 @@
       <c r="T10">
         <v>35550.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10">
+        <v>66003.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E11" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F11">
         <v>89.59999999999999</v>
@@ -4767,22 +4800,25 @@
       <c r="T11">
         <v>4530</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11">
+        <v>7073</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D12" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E12" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F12">
         <v>999.9</v>
@@ -4829,22 +4865,25 @@
       <c r="T12">
         <v>52070.7</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12">
+        <v>98684.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D13" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E13" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F13">
         <v>156</v>
@@ -4891,22 +4930,25 @@
       <c r="T13">
         <v>4873.3</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13">
+        <v>15988.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D14" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E14" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F14">
         <v>261.9</v>
@@ -4953,22 +4995,25 @@
       <c r="T14">
         <v>2281.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14">
+        <v>11437.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D15" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E15" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F15">
         <v>73.7</v>
@@ -5015,22 +5060,25 @@
       <c r="T15">
         <v>3293.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15">
+        <v>9324.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D16" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E16" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F16">
         <v>125.9</v>
@@ -5077,22 +5125,25 @@
       <c r="T16">
         <v>2495.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16">
+        <v>2451.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E17" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F17">
         <v>131</v>
@@ -5139,22 +5190,25 @@
       <c r="T17">
         <v>2294.7</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17">
+        <v>1544.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D18" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E18" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F18">
         <v>124.4</v>
@@ -5201,22 +5255,25 @@
       <c r="T18">
         <v>3723.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="U18">
+        <v>4772.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E19" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F19">
         <v>85</v>
@@ -5263,22 +5320,25 @@
       <c r="T19">
         <v>2381.1</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19">
+        <v>2668.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D20" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E20" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F20">
         <v>122.8</v>
@@ -5325,22 +5385,25 @@
       <c r="T20">
         <v>2563</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="U20">
+        <v>2811.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D21" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E21" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F21">
         <v>282.3</v>
@@ -5387,22 +5450,25 @@
       <c r="T21">
         <v>8363.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="U21">
+        <v>9571.700000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D22" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E22" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F22">
         <v>776.4</v>
@@ -5449,22 +5515,25 @@
       <c r="T22">
         <v>7069.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="U22">
+        <v>8185.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D23" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E23" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F23">
         <v>242</v>
@@ -5511,22 +5580,25 @@
       <c r="T23">
         <v>16884.2</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="U23">
+        <v>19000.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D24" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E24" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F24">
         <v>225.4</v>
@@ -5573,22 +5645,25 @@
       <c r="T24">
         <v>7364.3</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="U24">
+        <v>9680.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D25" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E25" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F25">
         <v>139.6</v>
@@ -5635,22 +5710,25 @@
       <c r="T25">
         <v>12982.4</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="U25">
+        <v>22738.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D26" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E26" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F26">
         <v>95.90000000000001</v>
@@ -5697,22 +5775,25 @@
       <c r="T26">
         <v>6417.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="U26">
+        <v>6439.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D27" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E27" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F27">
         <v>157.9</v>
@@ -5759,22 +5840,25 @@
       <c r="T27">
         <v>11252</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="U27">
+        <v>14078.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D28" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E28" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F28">
         <v>110.4</v>
@@ -5821,22 +5905,25 @@
       <c r="T28">
         <v>31599.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="U28">
+        <v>22443.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E29" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F29">
         <v>117.9</v>
@@ -5883,22 +5970,25 @@
       <c r="T29">
         <v>4466</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="U29">
+        <v>7674.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D30" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E30" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F30">
         <v>276.1</v>
@@ -5945,22 +6035,25 @@
       <c r="T30">
         <v>3265</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="U30">
+        <v>3439.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C31" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D31" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E31" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F31">
         <v>127.7</v>
@@ -6007,22 +6100,25 @@
       <c r="T31">
         <v>12124.8</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="U31">
+        <v>15991.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C32" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D32" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E32" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F32">
         <v>115.3</v>
@@ -6069,22 +6165,25 @@
       <c r="T32">
         <v>4354.2</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
+      <c r="U32">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C33" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D33" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E33" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F33">
         <v>72.3</v>
@@ -6131,22 +6230,25 @@
       <c r="T33">
         <v>11774.1</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="U33">
+        <v>4422.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C34" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D34" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E34" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F34">
         <v>83.59999999999999</v>
@@ -6193,22 +6295,25 @@
       <c r="T34">
         <v>7376.8</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
+      <c r="U34">
+        <v>7987.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C35" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D35" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E35" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F35">
         <v>101</v>
@@ -6255,22 +6360,25 @@
       <c r="T35">
         <v>2686.2</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
+      <c r="U35">
+        <v>4666.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C36" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D36" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E36" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F36">
         <v>103.3</v>
@@ -6317,22 +6425,25 @@
       <c r="T36">
         <v>4818.7</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
+      <c r="U36">
+        <v>7627.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C37" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D37" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E37" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F37">
         <v>131.9</v>
@@ -6379,22 +6490,25 @@
       <c r="T37">
         <v>8836.700000000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:20">
+      <c r="U37">
+        <v>22711.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C38" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D38" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E38" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F38">
         <v>1321.5</v>
@@ -6441,22 +6555,25 @@
       <c r="T38">
         <v>25073.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:20">
+      <c r="U38">
+        <v>21441.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C39" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D39" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E39" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F39">
         <v>547.9</v>
@@ -6503,22 +6620,25 @@
       <c r="T39">
         <v>23461.6</v>
       </c>
-    </row>
-    <row r="40" spans="1:20">
+      <c r="U39">
+        <v>29283.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C40" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D40" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E40" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F40">
         <v>2021.5</v>
@@ -6565,22 +6685,25 @@
       <c r="T40">
         <v>4489.2</v>
       </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="U40">
+        <v>14510.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D41" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E41" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F41">
         <v>1990.4</v>
@@ -6627,22 +6750,25 @@
       <c r="T41">
         <v>20792.2</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="U41">
+        <v>25607.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D42" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E42" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F42">
         <v>233.2</v>
@@ -6689,22 +6815,25 @@
       <c r="T42">
         <v>21213.8</v>
       </c>
-    </row>
-    <row r="43" spans="1:20">
+      <c r="U42">
+        <v>17525</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C43" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D43" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E43" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F43">
         <v>193.9</v>
@@ -6751,22 +6880,25 @@
       <c r="T43">
         <v>6608.2</v>
       </c>
-    </row>
-    <row r="44" spans="1:20">
+      <c r="U43">
+        <v>9770.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C44" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D44" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E44" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F44">
         <v>242.9</v>
@@ -6813,22 +6945,25 @@
       <c r="T44">
         <v>24354.7</v>
       </c>
-    </row>
-    <row r="45" spans="1:20">
+      <c r="U44">
+        <v>14312.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C45" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D45" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E45" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F45">
         <v>1410.2</v>
@@ -6875,22 +7010,25 @@
       <c r="T45">
         <v>21299.3</v>
       </c>
-    </row>
-    <row r="46" spans="1:20">
+      <c r="U45">
+        <v>29560.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C46" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D46" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E46" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F46">
         <v>164.1</v>
@@ -6937,22 +7075,25 @@
       <c r="T46">
         <v>75869.3</v>
       </c>
-    </row>
-    <row r="47" spans="1:20">
+      <c r="U46">
+        <v>42042.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C47" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D47" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E47" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F47">
         <v>6452.7</v>
@@ -6999,22 +7140,25 @@
       <c r="T47">
         <v>195521.8</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
+      <c r="U47">
+        <v>96405.60000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C48" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D48" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E48" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F48">
         <v>221.3</v>
@@ -7061,22 +7205,25 @@
       <c r="T48">
         <v>43316.3</v>
       </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="U48">
+        <v>12454.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C49" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D49" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E49" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F49">
         <v>1340.6</v>
@@ -7123,22 +7270,25 @@
       <c r="T49">
         <v>22885.7</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="U49">
+        <v>38311.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D50" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E50" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F50">
         <v>180.7</v>
@@ -7185,22 +7335,25 @@
       <c r="T50">
         <v>3230.8</v>
       </c>
-    </row>
-    <row r="51" spans="1:20">
+      <c r="U50">
+        <v>9051.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C51" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D51" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E51" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F51">
         <v>150.6</v>
@@ -7247,22 +7400,25 @@
       <c r="T51">
         <v>4184</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="U51">
+        <v>8743.799999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C52" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D52" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E52" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F52">
         <v>391.5</v>
@@ -7309,22 +7465,25 @@
       <c r="T52">
         <v>15445.3</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="U52">
+        <v>16568.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C53" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D53" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E53" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F53">
         <v>750.6</v>
@@ -7371,22 +7530,25 @@
       <c r="T53">
         <v>23300.6</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="U53">
+        <v>24355.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C54" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D54" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E54" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F54">
         <v>641.7</v>
@@ -7433,22 +7595,25 @@
       <c r="T54">
         <v>12094.7</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="U54">
+        <v>39923.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C55" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D55" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E55" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F55">
         <v>216.2</v>
@@ -7495,22 +7660,25 @@
       <c r="T55">
         <v>4862.2</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="U55">
+        <v>5336.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C56" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D56" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E56" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F56">
         <v>264.2</v>
@@ -7557,22 +7725,25 @@
       <c r="T56">
         <v>12463.9</v>
       </c>
-    </row>
-    <row r="57" spans="1:20">
+      <c r="U56">
+        <v>16396.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C57" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D57" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E57" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F57">
         <v>211.2</v>
@@ -7619,22 +7790,25 @@
       <c r="T57">
         <v>22929.1</v>
       </c>
-    </row>
-    <row r="58" spans="1:20">
+      <c r="U57">
+        <v>12034.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C58" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D58" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E58" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F58">
         <v>291.2</v>
@@ -7681,22 +7855,25 @@
       <c r="T58">
         <v>9094.200000000001</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58">
+        <v>11595.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C59" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D59" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E59" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F59">
         <v>245.9</v>
@@ -7743,22 +7920,25 @@
       <c r="T59">
         <v>12742.6</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59">
+        <v>4405.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C60" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D60" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E60" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F60">
         <v>228.1</v>
@@ -7805,22 +7985,25 @@
       <c r="T60">
         <v>4978.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60">
+        <v>6037.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C61" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D61" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E61" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F61">
         <v>181.1</v>
@@ -7867,22 +8050,25 @@
       <c r="T61">
         <v>15983.7</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61">
+        <v>17125.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C62" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D62" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E62" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F62">
         <v>243.4</v>
@@ -7929,22 +8115,25 @@
       <c r="T62">
         <v>24217.2</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62">
+        <v>15886</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C63" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D63" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E63" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F63">
         <v>200.2</v>
@@ -7991,22 +8180,25 @@
       <c r="T63">
         <v>6768</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63">
+        <v>14701.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D64" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E64" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F64">
         <v>232.7</v>
@@ -8053,22 +8245,25 @@
       <c r="T64">
         <v>31791.5</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
+      <c r="U64">
+        <v>55058.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C65" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D65" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E65" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F65">
         <v>347.8</v>
@@ -8115,22 +8310,25 @@
       <c r="T65">
         <v>4717.3</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="U65">
+        <v>28453.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C66" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D66" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E66" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F66">
         <v>678.5</v>
@@ -8177,22 +8375,25 @@
       <c r="T66">
         <v>9856.299999999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="U66">
+        <v>10913.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D67" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E67" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F67">
         <v>1113.1</v>
@@ -8239,22 +8440,25 @@
       <c r="T67">
         <v>15328.8</v>
       </c>
-    </row>
-    <row r="68" spans="1:20">
+      <c r="U67">
+        <v>21839.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C68" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D68" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E68" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8301,22 +8505,25 @@
       <c r="T68">
         <v>5804.4</v>
       </c>
-    </row>
-    <row r="69" spans="1:20">
+      <c r="U68">
+        <v>3193.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C69" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D69" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E69" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -8363,22 +8570,25 @@
       <c r="T69">
         <v>2519.9</v>
       </c>
-    </row>
-    <row r="70" spans="1:20">
+      <c r="U69">
+        <v>4766.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C70" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D70" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E70" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F70">
         <v>1180.1</v>
@@ -8425,22 +8635,25 @@
       <c r="T70">
         <v>15259</v>
       </c>
-    </row>
-    <row r="71" spans="1:20">
+      <c r="U70">
+        <v>21480.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C71" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D71" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E71" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F71">
         <v>1029.4</v>
@@ -8487,22 +8700,25 @@
       <c r="T71">
         <v>3248.1</v>
       </c>
-    </row>
-    <row r="72" spans="1:20">
+      <c r="U71">
+        <v>11076.6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C72" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D72" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E72" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F72">
         <v>100.9</v>
@@ -8549,22 +8765,25 @@
       <c r="T72">
         <v>1706.3</v>
       </c>
-    </row>
-    <row r="73" spans="1:20">
+      <c r="U72">
+        <v>3102.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C73" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D73" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E73" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F73">
         <v>242.5</v>
@@ -8611,22 +8830,25 @@
       <c r="T73">
         <v>2752.5</v>
       </c>
-    </row>
-    <row r="74" spans="1:20">
+      <c r="U73">
+        <v>6019.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C74" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D74" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E74" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F74">
         <v>201</v>
@@ -8673,22 +8895,25 @@
       <c r="T74">
         <v>1539.3</v>
       </c>
-    </row>
-    <row r="75" spans="1:20">
+      <c r="U74">
+        <v>6268.9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B75" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C75" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D75" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E75" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F75">
         <v>132.8</v>
@@ -8735,22 +8960,25 @@
       <c r="T75">
         <v>3845.1</v>
       </c>
-    </row>
-    <row r="76" spans="1:20">
+      <c r="U75">
+        <v>3520.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C76" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D76" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E76" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F76">
         <v>2779.7</v>
@@ -8797,22 +9025,25 @@
       <c r="T76">
         <v>4061.8</v>
       </c>
-    </row>
-    <row r="77" spans="1:20">
+      <c r="U76">
+        <v>11661.2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B77" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C77" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D77" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E77" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F77">
         <v>6245.5</v>
@@ -8859,22 +9090,25 @@
       <c r="T77">
         <v>63529.7</v>
       </c>
-    </row>
-    <row r="78" spans="1:20">
+      <c r="U77">
+        <v>68010.89999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C78" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D78" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E78" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F78">
         <v>759</v>
@@ -8921,22 +9155,25 @@
       <c r="T78">
         <v>76882.39999999999</v>
       </c>
-    </row>
-    <row r="79" spans="1:20">
+      <c r="U78">
+        <v>44675.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C79" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D79" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E79" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F79">
         <v>153.8</v>
@@ -8983,22 +9220,25 @@
       <c r="T79">
         <v>3859.6</v>
       </c>
-    </row>
-    <row r="80" spans="1:20">
+      <c r="U79">
+        <v>3991.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B80" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C80" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D80" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E80" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F80">
         <v>83.3</v>
@@ -9045,22 +9285,25 @@
       <c r="T80">
         <v>2745.6</v>
       </c>
-    </row>
-    <row r="81" spans="1:20">
+      <c r="U80">
+        <v>3180.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B81" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C81" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D81" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E81" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F81">
         <v>191.8</v>
@@ -9107,22 +9350,25 @@
       <c r="T81">
         <v>4003.5</v>
       </c>
-    </row>
-    <row r="82" spans="1:20">
+      <c r="U81">
+        <v>4542.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B82" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C82" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D82" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E82" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F82">
         <v>194.4</v>
@@ -9169,22 +9415,25 @@
       <c r="T82">
         <v>2657.8</v>
       </c>
-    </row>
-    <row r="83" spans="1:20">
+      <c r="U82">
+        <v>3372.8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B83" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C83" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D83" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E83" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F83">
         <v>2031</v>
@@ -9231,22 +9480,25 @@
       <c r="T83">
         <v>30921.8</v>
       </c>
-    </row>
-    <row r="84" spans="1:20">
+      <c r="U83">
+        <v>39698</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B84" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C84" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D84" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E84" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F84">
         <v>1129.1</v>
@@ -9293,22 +9545,25 @@
       <c r="T84">
         <v>34173.7</v>
       </c>
-    </row>
-    <row r="85" spans="1:20">
+      <c r="U84">
+        <v>36956.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B85" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C85" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D85" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E85" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F85">
         <v>2037.3</v>
@@ -9355,22 +9610,25 @@
       <c r="T85">
         <v>13149.8</v>
       </c>
-    </row>
-    <row r="86" spans="1:20">
+      <c r="U85">
+        <v>10232.7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B86" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C86" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D86" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E86" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9417,22 +9675,25 @@
       <c r="T86">
         <v>35087.2</v>
       </c>
-    </row>
-    <row r="87" spans="1:20">
+      <c r="U86">
+        <v>97818.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B87" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C87" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D87" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E87" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F87">
         <v>239.5</v>
@@ -9479,22 +9740,25 @@
       <c r="T87">
         <v>30216.4</v>
       </c>
-    </row>
-    <row r="88" spans="1:20">
+      <c r="U87">
+        <v>75731.3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B88" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C88" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D88" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E88" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F88">
         <v>240.6</v>
@@ -9541,22 +9805,25 @@
       <c r="T88">
         <v>6451.5</v>
       </c>
-    </row>
-    <row r="89" spans="1:20">
+      <c r="U88">
+        <v>7570.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C89" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D89" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E89" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F89">
         <v>306.4</v>
@@ -9603,22 +9870,25 @@
       <c r="T89">
         <v>6171</v>
       </c>
-    </row>
-    <row r="90" spans="1:20">
+      <c r="U89">
+        <v>14029</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C90" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D90" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E90" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F90">
         <v>1824.9</v>
@@ -9665,22 +9935,25 @@
       <c r="T90">
         <v>45072.8</v>
       </c>
-    </row>
-    <row r="91" spans="1:20">
+      <c r="U90">
+        <v>64850.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B91" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C91" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D91" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E91" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F91">
         <v>324.1</v>
@@ -9727,22 +10000,25 @@
       <c r="T91">
         <v>37855.8</v>
       </c>
-    </row>
-    <row r="92" spans="1:20">
+      <c r="U91">
+        <v>97065</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C92" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D92" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E92" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F92">
         <v>409.8</v>
@@ -9789,22 +10065,25 @@
       <c r="T92">
         <v>741666.5</v>
       </c>
-    </row>
-    <row r="93" spans="1:20">
+      <c r="U92">
+        <v>365288.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B93" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C93" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D93" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E93" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F93">
         <v>4170.2</v>
@@ -9851,22 +10130,25 @@
       <c r="T93">
         <v>39242.2</v>
       </c>
-    </row>
-    <row r="94" spans="1:20">
+      <c r="U93">
+        <v>107307.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B94" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C94" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D94" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E94" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F94">
         <v>134.6</v>
@@ -9913,22 +10195,25 @@
       <c r="T94">
         <v>3753.3</v>
       </c>
-    </row>
-    <row r="95" spans="1:20">
+      <c r="U94">
+        <v>8887.700000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B95" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C95" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D95" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E95" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F95">
         <v>290</v>
@@ -9975,22 +10260,25 @@
       <c r="T95">
         <v>17500.2</v>
       </c>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95">
+        <v>19842.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C96" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D96" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E96" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F96">
         <v>705.9</v>
@@ -10037,22 +10325,25 @@
       <c r="T96">
         <v>34993.3</v>
       </c>
-    </row>
-    <row r="97" spans="1:20">
+      <c r="U96">
+        <v>28433.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B97" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C97" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D97" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E97" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F97">
         <v>109.2</v>
@@ -10099,22 +10390,25 @@
       <c r="T97">
         <v>8126.6</v>
       </c>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="U97">
+        <v>14088.9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B98" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C98" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D98" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E98" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F98">
         <v>252.4</v>
@@ -10161,22 +10455,25 @@
       <c r="T98">
         <v>7224.2</v>
       </c>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="U98">
+        <v>11123.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C99" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D99" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E99" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F99">
         <v>216</v>
@@ -10223,22 +10520,25 @@
       <c r="T99">
         <v>13097.2</v>
       </c>
-    </row>
-    <row r="100" spans="1:20">
+      <c r="U99">
+        <v>16568.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B100" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D100" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E100" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F100">
         <v>137.9</v>
@@ -10285,22 +10585,25 @@
       <c r="T100">
         <v>7805.4</v>
       </c>
-    </row>
-    <row r="101" spans="1:20">
+      <c r="U100">
+        <v>12113.9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C101" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D101" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E101" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F101">
         <v>165.3</v>
@@ -10347,22 +10650,25 @@
       <c r="T101">
         <v>30493</v>
       </c>
-    </row>
-    <row r="102" spans="1:20">
+      <c r="U101">
+        <v>41004.2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B102" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C102" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D102" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E102" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F102">
         <v>161.4</v>
@@ -10409,22 +10715,25 @@
       <c r="T102">
         <v>14509.3</v>
       </c>
-    </row>
-    <row r="103" spans="1:20">
+      <c r="U102">
+        <v>27278</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C103" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D103" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E103" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F103">
         <v>159.3</v>
@@ -10471,22 +10780,25 @@
       <c r="T103">
         <v>8098.2</v>
       </c>
-    </row>
-    <row r="104" spans="1:20">
+      <c r="U103">
+        <v>15008.4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B104" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C104" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D104" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E104" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F104">
         <v>223.1</v>
@@ -10533,22 +10845,25 @@
       <c r="T104">
         <v>9633.1</v>
       </c>
-    </row>
-    <row r="105" spans="1:20">
+      <c r="U104">
+        <v>10774.6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B105" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C105" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D105" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E105" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F105">
         <v>146.2</v>
@@ -10595,22 +10910,25 @@
       <c r="T105">
         <v>9190</v>
       </c>
-    </row>
-    <row r="106" spans="1:20">
+      <c r="U105">
+        <v>8462.200000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B106" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C106" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D106" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E106" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F106">
         <v>229.5</v>
@@ -10657,22 +10975,25 @@
       <c r="T106">
         <v>14664.1</v>
       </c>
-    </row>
-    <row r="107" spans="1:20">
+      <c r="U106">
+        <v>14689.2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B107" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C107" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D107" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E107" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F107">
         <v>232.2</v>
@@ -10719,22 +11040,25 @@
       <c r="T107">
         <v>8603.5</v>
       </c>
-    </row>
-    <row r="108" spans="1:20">
+      <c r="U107">
+        <v>14270.1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B108" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C108" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D108" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E108" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F108">
         <v>344</v>
@@ -10781,22 +11105,25 @@
       <c r="T108">
         <v>6806.4</v>
       </c>
-    </row>
-    <row r="109" spans="1:20">
+      <c r="U108">
+        <v>8308</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B109" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C109" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D109" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E109" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F109">
         <v>753.5</v>
@@ -10843,22 +11170,25 @@
       <c r="T109">
         <v>15797</v>
       </c>
-    </row>
-    <row r="110" spans="1:20">
+      <c r="U109">
+        <v>12564.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21">
       <c r="A110" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B110" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C110" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D110" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E110" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F110">
         <v>56</v>
@@ -10905,22 +11235,25 @@
       <c r="T110">
         <v>6330.6</v>
       </c>
-    </row>
-    <row r="111" spans="1:20">
+      <c r="U110">
+        <v>13545.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21">
       <c r="A111" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C111" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D111" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E111" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F111">
         <v>195.7</v>
@@ -10967,22 +11300,25 @@
       <c r="T111">
         <v>4647.9</v>
       </c>
-    </row>
-    <row r="112" spans="1:20">
+      <c r="U111">
+        <v>5857.9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21">
       <c r="A112" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C112" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D112" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E112" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F112">
         <v>132.5</v>
@@ -11029,22 +11365,25 @@
       <c r="T112">
         <v>4945.8</v>
       </c>
-    </row>
-    <row r="113" spans="1:20">
+      <c r="U112">
+        <v>5878.7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C113" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D113" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E113" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F113">
         <v>172.5</v>
@@ -11091,22 +11430,25 @@
       <c r="T113">
         <v>7827.1</v>
       </c>
-    </row>
-    <row r="114" spans="1:20">
+      <c r="U113">
+        <v>6521.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
       <c r="A114" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C114" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D114" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E114" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F114">
         <v>108.5</v>
@@ -11153,22 +11495,25 @@
       <c r="T114">
         <v>2238.4</v>
       </c>
-    </row>
-    <row r="115" spans="1:20">
+      <c r="U114">
+        <v>4429.8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
       <c r="A115" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B115" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C115" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D115" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E115" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F115">
         <v>105.8</v>
@@ -11215,22 +11560,25 @@
       <c r="T115">
         <v>4990</v>
       </c>
-    </row>
-    <row r="116" spans="1:20">
+      <c r="U115">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21">
       <c r="A116" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B116" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C116" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D116" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E116" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F116">
         <v>1642.3</v>
@@ -11277,22 +11625,25 @@
       <c r="T116">
         <v>6975.7</v>
       </c>
-    </row>
-    <row r="117" spans="1:20">
+      <c r="U116">
+        <v>10223</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
       <c r="A117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B117" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C117" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D117" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E117" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F117">
         <v>154.1</v>
@@ -11339,22 +11690,25 @@
       <c r="T117">
         <v>3243.5</v>
       </c>
-    </row>
-    <row r="118" spans="1:20">
+      <c r="U117">
+        <v>4437.9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
       <c r="A118" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B118" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C118" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D118" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E118" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F118">
         <v>161.7</v>
@@ -11401,22 +11755,25 @@
       <c r="T118">
         <v>5867.6</v>
       </c>
-    </row>
-    <row r="119" spans="1:20">
+      <c r="U118">
+        <v>5613.3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C119" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D119" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E119" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F119">
         <v>61.5</v>
@@ -11463,22 +11820,25 @@
       <c r="T119">
         <v>5652</v>
       </c>
-    </row>
-    <row r="120" spans="1:20">
+      <c r="U119">
+        <v>4947.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B120" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C120" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D120" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E120" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F120">
         <v>270</v>
@@ -11525,22 +11885,25 @@
       <c r="T120">
         <v>4119.2</v>
       </c>
-    </row>
-    <row r="121" spans="1:20">
+      <c r="U120">
+        <v>7180.8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C121" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D121" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E121" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F121">
         <v>81.3</v>
@@ -11587,22 +11950,25 @@
       <c r="T121">
         <v>8058.3</v>
       </c>
-    </row>
-    <row r="122" spans="1:20">
+      <c r="U121">
+        <v>7171.9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C122" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D122" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E122" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F122">
         <v>313.7</v>
@@ -11649,22 +12015,25 @@
       <c r="T122">
         <v>17285.8</v>
       </c>
-    </row>
-    <row r="123" spans="1:20">
+      <c r="U122">
+        <v>53042.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C123" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D123" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E123" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F123">
         <v>210.9</v>
@@ -11711,22 +12080,25 @@
       <c r="T123">
         <v>2206</v>
       </c>
-    </row>
-    <row r="124" spans="1:20">
+      <c r="U123">
+        <v>2429.3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
       <c r="A124" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B124" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C124" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D124" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E124" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F124">
         <v>159.4</v>
@@ -11773,22 +12145,25 @@
       <c r="T124">
         <v>4852.6</v>
       </c>
-    </row>
-    <row r="125" spans="1:20">
+      <c r="U124">
+        <v>7110.8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
       <c r="A125" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C125" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D125" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E125" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F125">
         <v>312.7</v>
@@ -11835,22 +12210,25 @@
       <c r="T125">
         <v>5699.5</v>
       </c>
-    </row>
-    <row r="126" spans="1:20">
+      <c r="U125">
+        <v>7484.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
       <c r="A126" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B126" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C126" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D126" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E126" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F126">
         <v>355</v>
@@ -11897,22 +12275,25 @@
       <c r="T126">
         <v>7962.2</v>
       </c>
-    </row>
-    <row r="127" spans="1:20">
+      <c r="U126">
+        <v>9925.200000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B127" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C127" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D127" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E127" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F127">
         <v>229.5</v>
@@ -11959,22 +12340,25 @@
       <c r="T127">
         <v>3624.7</v>
       </c>
-    </row>
-    <row r="128" spans="1:20">
+      <c r="U127">
+        <v>3907.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
       <c r="A128" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C128" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D128" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E128" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F128">
         <v>178.9</v>
@@ -12021,22 +12405,25 @@
       <c r="T128">
         <v>3730</v>
       </c>
-    </row>
-    <row r="129" spans="1:20">
+      <c r="U128">
+        <v>5418.1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B129" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C129" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D129" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E129" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -12083,22 +12470,25 @@
       <c r="T129">
         <v>3429.8</v>
       </c>
-    </row>
-    <row r="130" spans="1:20">
+      <c r="U129">
+        <v>8944.799999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21">
       <c r="A130" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B130" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C130" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D130" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E130" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F130">
         <v>990</v>
@@ -12145,22 +12535,25 @@
       <c r="T130">
         <v>44079.1</v>
       </c>
-    </row>
-    <row r="131" spans="1:20">
+      <c r="U130">
+        <v>24541.7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21">
       <c r="A131" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B131" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C131" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D131" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E131" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F131">
         <v>179.1</v>
@@ -12207,22 +12600,25 @@
       <c r="T131">
         <v>3182</v>
       </c>
-    </row>
-    <row r="132" spans="1:20">
+      <c r="U131">
+        <v>6751.7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21">
       <c r="A132" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B132" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C132" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D132" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E132" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F132">
         <v>116.4</v>
@@ -12269,22 +12665,25 @@
       <c r="T132">
         <v>2337.3</v>
       </c>
-    </row>
-    <row r="133" spans="1:20">
+      <c r="U132">
+        <v>2745.8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21">
       <c r="A133" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B133" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C133" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D133" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E133" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F133">
         <v>267.1</v>
@@ -12331,22 +12730,25 @@
       <c r="T133">
         <v>3121.4</v>
       </c>
-    </row>
-    <row r="134" spans="1:20">
+      <c r="U133">
+        <v>6024.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21">
       <c r="A134" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C134" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D134" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E134" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F134">
         <v>235.6</v>
@@ -12393,22 +12795,25 @@
       <c r="T134">
         <v>2019.8</v>
       </c>
-    </row>
-    <row r="135" spans="1:20">
+      <c r="U134">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21">
       <c r="A135" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B135" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D135" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E135" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F135">
         <v>168.1</v>
@@ -12455,22 +12860,25 @@
       <c r="T135">
         <v>2363.2</v>
       </c>
-    </row>
-    <row r="136" spans="1:20">
+      <c r="U135">
+        <v>9108.200000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B136" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C136" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D136" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E136" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F136">
         <v>611</v>
@@ -12517,22 +12925,25 @@
       <c r="T136">
         <v>5432.4</v>
       </c>
-    </row>
-    <row r="137" spans="1:20">
+      <c r="U136">
+        <v>11416.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21">
       <c r="A137" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B137" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C137" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D137" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E137" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F137">
         <v>371.8</v>
@@ -12579,22 +12990,25 @@
       <c r="T137">
         <v>18690.3</v>
       </c>
-    </row>
-    <row r="138" spans="1:20">
+      <c r="U137">
+        <v>28778.7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21">
       <c r="A138" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B138" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C138" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D138" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E138" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F138">
         <v>146.2</v>
@@ -12641,22 +13055,25 @@
       <c r="T138">
         <v>1552.5</v>
       </c>
-    </row>
-    <row r="139" spans="1:20">
+      <c r="U138">
+        <v>5552</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B139" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C139" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D139" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E139" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F139">
         <v>160.5</v>
@@ -12703,22 +13120,25 @@
       <c r="T139">
         <v>4297.9</v>
       </c>
-    </row>
-    <row r="140" spans="1:20">
+      <c r="U139">
+        <v>5186.6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B140" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C140" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D140" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E140" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F140">
         <v>130.6</v>
@@ -12765,22 +13185,25 @@
       <c r="T140">
         <v>3262.8</v>
       </c>
-    </row>
-    <row r="141" spans="1:20">
+      <c r="U140">
+        <v>4750.6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21">
       <c r="A141" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B141" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C141" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D141" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E141" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F141">
         <v>564.3</v>
@@ -12827,22 +13250,25 @@
       <c r="T141">
         <v>12365.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:20">
+      <c r="U141">
+        <v>18607.4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21">
       <c r="A142" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B142" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C142" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D142" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E142" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F142">
         <v>751.9</v>
@@ -12889,22 +13315,25 @@
       <c r="T142">
         <v>13848.8</v>
       </c>
-    </row>
-    <row r="143" spans="1:20">
+      <c r="U142">
+        <v>14876</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C143" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D143" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E143" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F143">
         <v>3581.6</v>
@@ -12951,22 +13380,25 @@
       <c r="T143">
         <v>177691.6</v>
       </c>
-    </row>
-    <row r="144" spans="1:20">
+      <c r="U143">
+        <v>168088.3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21">
       <c r="A144" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B144" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C144" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D144" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E144" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F144">
         <v>1042.6</v>
@@ -13013,22 +13445,25 @@
       <c r="T144">
         <v>17905.1</v>
       </c>
-    </row>
-    <row r="145" spans="1:20">
+      <c r="U144">
+        <v>64887.4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B145" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C145" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D145" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E145" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F145">
         <v>210.8</v>
@@ -13075,22 +13510,25 @@
       <c r="T145">
         <v>7922.4</v>
       </c>
-    </row>
-    <row r="146" spans="1:20">
+      <c r="U145">
+        <v>23622.3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B146" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C146" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D146" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E146" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F146">
         <v>212.2</v>
@@ -13137,22 +13575,25 @@
       <c r="T146">
         <v>12141.3</v>
       </c>
-    </row>
-    <row r="147" spans="1:20">
+      <c r="U146">
+        <v>10218.4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21">
       <c r="A147" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B147" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C147" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D147" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E147" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F147">
         <v>336.2</v>
@@ -13199,22 +13640,25 @@
       <c r="T147">
         <v>5731.6</v>
       </c>
-    </row>
-    <row r="148" spans="1:20">
+      <c r="U147">
+        <v>20884.8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B148" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C148" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D148" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E148" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F148">
         <v>323.6</v>
@@ -13261,22 +13705,25 @@
       <c r="T148">
         <v>3383.8</v>
       </c>
-    </row>
-    <row r="149" spans="1:20">
+      <c r="U148">
+        <v>6608.6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21">
       <c r="A149" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C149" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D149" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E149" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F149">
         <v>1016</v>
@@ -13323,22 +13770,25 @@
       <c r="T149">
         <v>10939</v>
       </c>
-    </row>
-    <row r="150" spans="1:20">
+      <c r="U149">
+        <v>14486.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21">
       <c r="A150" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B150" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C150" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D150" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E150" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F150">
         <v>228.8</v>
@@ -13385,22 +13835,25 @@
       <c r="T150">
         <v>4847</v>
       </c>
-    </row>
-    <row r="151" spans="1:20">
+      <c r="U150">
+        <v>10807.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B151" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C151" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D151" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E151" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F151">
         <v>751.8</v>
@@ -13447,22 +13900,25 @@
       <c r="T151">
         <v>7919.1</v>
       </c>
-    </row>
-    <row r="152" spans="1:20">
+      <c r="U151">
+        <v>10801.2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B152" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C152" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D152" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E152" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F152">
         <v>314.5</v>
@@ -13509,22 +13965,25 @@
       <c r="T152">
         <v>5175.8</v>
       </c>
-    </row>
-    <row r="153" spans="1:20">
+      <c r="U152">
+        <v>8350.700000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C153" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D153" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E153" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F153">
         <v>618.2</v>
@@ -13571,22 +14030,25 @@
       <c r="T153">
         <v>23806.1</v>
       </c>
-    </row>
-    <row r="154" spans="1:20">
+      <c r="U153">
+        <v>23698.6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B154" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C154" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D154" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E154" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -13633,22 +14095,25 @@
       <c r="T154">
         <v>48355.5</v>
       </c>
-    </row>
-    <row r="155" spans="1:20">
+      <c r="U154">
+        <v>48552.7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21">
       <c r="A155" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C155" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D155" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E155" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F155">
         <v>40.3</v>
@@ -13695,22 +14160,25 @@
       <c r="T155">
         <v>167330.6</v>
       </c>
-    </row>
-    <row r="156" spans="1:20">
+      <c r="U155">
+        <v>83194.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21">
       <c r="A156" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B156" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C156" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D156" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E156" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F156">
         <v>102.8</v>
@@ -13757,22 +14225,25 @@
       <c r="T156">
         <v>23919.9</v>
       </c>
-    </row>
-    <row r="157" spans="1:20">
+      <c r="U156">
+        <v>16860</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21">
       <c r="A157" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C157" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D157" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E157" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F157">
         <v>60.4</v>
@@ -13819,22 +14290,25 @@
       <c r="T157">
         <v>28408</v>
       </c>
-    </row>
-    <row r="158" spans="1:20">
+      <c r="U157">
+        <v>12842.1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21">
       <c r="A158" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B158" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C158" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D158" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E158" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F158">
         <v>144.2</v>
@@ -13881,22 +14355,25 @@
       <c r="T158">
         <v>18751.7</v>
       </c>
-    </row>
-    <row r="159" spans="1:20">
+      <c r="U158">
+        <v>24421.6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21">
       <c r="A159" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B159" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C159" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D159" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E159" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -13943,22 +14420,25 @@
       <c r="T159">
         <v>27280.3</v>
       </c>
-    </row>
-    <row r="160" spans="1:20">
+      <c r="U159">
+        <v>29312.2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21">
       <c r="A160" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B160" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C160" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D160" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E160" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -14005,22 +14485,25 @@
       <c r="T160">
         <v>8702.700000000001</v>
       </c>
-    </row>
-    <row r="161" spans="1:20">
+      <c r="U160">
+        <v>15961.6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21">
       <c r="A161" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B161" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C161" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D161" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E161" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F161">
         <v>415.8</v>
@@ -14067,22 +14550,25 @@
       <c r="T161">
         <v>11780.5</v>
       </c>
-    </row>
-    <row r="162" spans="1:20">
+      <c r="U161">
+        <v>11557.9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21">
       <c r="A162" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B162" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C162" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D162" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E162" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F162">
         <v>207.5</v>
@@ -14129,22 +14615,25 @@
       <c r="T162">
         <v>26957.3</v>
       </c>
-    </row>
-    <row r="163" spans="1:20">
+      <c r="U162">
+        <v>45892.4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21">
       <c r="A163" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B163" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C163" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D163" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E163" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F163">
         <v>590.5</v>
@@ -14191,22 +14680,25 @@
       <c r="T163">
         <v>4077.5</v>
       </c>
-    </row>
-    <row r="164" spans="1:20">
+      <c r="U163">
+        <v>2824.8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21">
       <c r="A164" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B164" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C164" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D164" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E164" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F164">
         <v>231.4</v>
@@ -14253,22 +14745,25 @@
       <c r="T164">
         <v>18543.8</v>
       </c>
-    </row>
-    <row r="165" spans="1:20">
+      <c r="U164">
+        <v>36552.1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21">
       <c r="A165" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B165" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C165" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D165" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E165" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F165">
         <v>457.1</v>
@@ -14315,22 +14810,25 @@
       <c r="T165">
         <v>5141.4</v>
       </c>
-    </row>
-    <row r="166" spans="1:20">
+      <c r="U165">
+        <v>23238.8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21">
       <c r="A166" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B166" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C166" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D166" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E166" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F166">
         <v>408.5</v>
@@ -14377,22 +14875,25 @@
       <c r="T166">
         <v>15334.3</v>
       </c>
-    </row>
-    <row r="167" spans="1:20">
+      <c r="U166">
+        <v>17483.6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21">
       <c r="A167" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B167" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C167" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D167" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E167" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F167">
         <v>112.3</v>
@@ -14439,22 +14940,25 @@
       <c r="T167">
         <v>15156.6</v>
       </c>
-    </row>
-    <row r="168" spans="1:20">
+      <c r="U167">
+        <v>22788.2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21">
       <c r="A168" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C168" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D168" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E168" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F168">
         <v>360.1</v>
@@ -14501,22 +15005,25 @@
       <c r="T168">
         <v>40609.4</v>
       </c>
-    </row>
-    <row r="169" spans="1:20">
+      <c r="U168">
+        <v>59327.7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21">
       <c r="A169" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B169" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C169" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D169" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E169" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F169">
         <v>126.2</v>
@@ -14563,22 +15070,25 @@
       <c r="T169">
         <v>23295.9</v>
       </c>
-    </row>
-    <row r="170" spans="1:20">
+      <c r="U169">
+        <v>11663.7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21">
       <c r="A170" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C170" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D170" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E170" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F170">
         <v>394.3</v>
@@ -14625,22 +15135,25 @@
       <c r="T170">
         <v>2411.6</v>
       </c>
-    </row>
-    <row r="171" spans="1:20">
+      <c r="U170">
+        <v>8128</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21">
       <c r="A171" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B171" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C171" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D171" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E171" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F171">
         <v>517</v>
@@ -14687,22 +15200,25 @@
       <c r="T171">
         <v>11202.7</v>
       </c>
-    </row>
-    <row r="172" spans="1:20">
+      <c r="U171">
+        <v>37619</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21">
       <c r="A172" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B172" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C172" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D172" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E172" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F172">
         <v>568.4</v>
@@ -14749,22 +15265,25 @@
       <c r="T172">
         <v>12270.9</v>
       </c>
-    </row>
-    <row r="173" spans="1:20">
+      <c r="U172">
+        <v>11737.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21">
       <c r="A173" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B173" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C173" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D173" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E173" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F173">
         <v>426.3</v>
@@ -14811,22 +15330,25 @@
       <c r="T173">
         <v>12161</v>
       </c>
-    </row>
-    <row r="174" spans="1:20">
+      <c r="U173">
+        <v>10955.8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21">
       <c r="A174" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B174" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C174" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D174" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E174" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F174">
         <v>225.9</v>
@@ -14873,22 +15395,25 @@
       <c r="T174">
         <v>15330.3</v>
       </c>
-    </row>
-    <row r="175" spans="1:20">
+      <c r="U174">
+        <v>13164.2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21">
       <c r="A175" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B175" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C175" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D175" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E175" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -14935,22 +15460,25 @@
       <c r="T175">
         <v>9273.9</v>
       </c>
-    </row>
-    <row r="176" spans="1:20">
+      <c r="U175">
+        <v>12627.1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21">
       <c r="A176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B176" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C176" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D176" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E176" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F176">
         <v>300.1</v>
@@ -14997,22 +15525,25 @@
       <c r="T176">
         <v>5250.3</v>
       </c>
-    </row>
-    <row r="177" spans="1:20">
+      <c r="U176">
+        <v>8749.4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21">
       <c r="A177" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B177" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C177" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D177" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E177" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F177">
         <v>1056.1</v>
@@ -15059,22 +15590,25 @@
       <c r="T177">
         <v>15943.4</v>
       </c>
-    </row>
-    <row r="178" spans="1:20">
+      <c r="U177">
+        <v>30828.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B178" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C178" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D178" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E178" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F178">
         <v>660.5</v>
@@ -15121,22 +15655,25 @@
       <c r="T178">
         <v>6285.3</v>
       </c>
-    </row>
-    <row r="179" spans="1:20">
+      <c r="U178">
+        <v>13629.7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21">
       <c r="A179" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B179" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C179" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D179" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E179" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F179">
         <v>308</v>
@@ -15183,22 +15720,25 @@
       <c r="T179">
         <v>11021.5</v>
       </c>
-    </row>
-    <row r="180" spans="1:20">
+      <c r="U179">
+        <v>17289.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B180" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C180" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D180" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E180" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F180">
         <v>198.5</v>
@@ -15245,22 +15785,25 @@
       <c r="T180">
         <v>2636.7</v>
       </c>
-    </row>
-    <row r="181" spans="1:20">
+      <c r="U180">
+        <v>5018.8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B181" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C181" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D181" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E181" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F181">
         <v>181.7</v>
@@ -15307,22 +15850,25 @@
       <c r="T181">
         <v>3433</v>
       </c>
-    </row>
-    <row r="182" spans="1:20">
+      <c r="U181">
+        <v>2907.2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B182" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C182" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D182" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E182" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F182">
         <v>355.9</v>
@@ -15369,22 +15915,25 @@
       <c r="T182">
         <v>3663</v>
       </c>
-    </row>
-    <row r="183" spans="1:20">
+      <c r="U182">
+        <v>6858.9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21">
       <c r="A183" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B183" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C183" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D183" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E183" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F183">
         <v>139.7</v>
@@ -15431,22 +15980,25 @@
       <c r="T183">
         <v>2199.5</v>
       </c>
-    </row>
-    <row r="184" spans="1:20">
+      <c r="U183">
+        <v>2703.3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21">
       <c r="A184" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B184" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C184" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D184" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E184" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F184">
         <v>102.2</v>
@@ -15493,22 +16045,25 @@
       <c r="T184">
         <v>2170.4</v>
       </c>
-    </row>
-    <row r="185" spans="1:20">
+      <c r="U184">
+        <v>2897.7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21">
       <c r="A185" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B185" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C185" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D185" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E185" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F185">
         <v>201.6</v>
@@ -15555,22 +16110,25 @@
       <c r="T185">
         <v>1838</v>
       </c>
-    </row>
-    <row r="186" spans="1:20">
+      <c r="U185">
+        <v>12761.8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21">
       <c r="A186" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C186" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D186" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E186" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F186">
         <v>84.7</v>
@@ -15617,22 +16175,25 @@
       <c r="T186">
         <v>1493.2</v>
       </c>
-    </row>
-    <row r="187" spans="1:20">
+      <c r="U186">
+        <v>3686.4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21">
       <c r="A187" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C187" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D187" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E187" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F187">
         <v>120.1</v>
@@ -15679,22 +16240,25 @@
       <c r="T187">
         <v>7748.6</v>
       </c>
-    </row>
-    <row r="188" spans="1:20">
+      <c r="U187">
+        <v>13342.7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21">
       <c r="A188" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B188" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C188" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D188" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E188" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F188">
         <v>175.5</v>
@@ -15741,22 +16305,25 @@
       <c r="T188">
         <v>1706.5</v>
       </c>
-    </row>
-    <row r="189" spans="1:20">
+      <c r="U188">
+        <v>2276.8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21">
       <c r="A189" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B189" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C189" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D189" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E189" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F189">
         <v>181.8</v>
@@ -15803,22 +16370,25 @@
       <c r="T189">
         <v>3430.6</v>
       </c>
-    </row>
-    <row r="190" spans="1:20">
+      <c r="U189">
+        <v>2222.1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21">
       <c r="A190" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B190" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C190" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D190" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E190" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F190">
         <v>254.8</v>
@@ -15865,22 +16435,25 @@
       <c r="T190">
         <v>4769.2</v>
       </c>
-    </row>
-    <row r="191" spans="1:20">
+      <c r="U190">
+        <v>3978.8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21">
       <c r="A191" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B191" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C191" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D191" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E191" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F191">
         <v>132.2</v>
@@ -15927,22 +16500,25 @@
       <c r="T191">
         <v>9687.5</v>
       </c>
-    </row>
-    <row r="192" spans="1:20">
+      <c r="U191">
+        <v>9183.200000000001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21">
       <c r="A192" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B192" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C192" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D192" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E192" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F192">
         <v>119.3</v>
@@ -15989,22 +16565,25 @@
       <c r="T192">
         <v>6947.3</v>
       </c>
-    </row>
-    <row r="193" spans="1:20">
+      <c r="U192">
+        <v>7582.1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21">
       <c r="A193" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B193" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C193" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D193" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E193" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F193">
         <v>186.2</v>
@@ -16051,22 +16630,25 @@
       <c r="T193">
         <v>4646</v>
       </c>
-    </row>
-    <row r="194" spans="1:20">
+      <c r="U193">
+        <v>7168.9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21">
       <c r="A194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B194" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C194" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D194" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E194" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F194">
         <v>98.40000000000001</v>
@@ -16113,22 +16695,25 @@
       <c r="T194">
         <v>3348.1</v>
       </c>
-    </row>
-    <row r="195" spans="1:20">
+      <c r="U194">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21">
       <c r="A195" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B195" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C195" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D195" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E195" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F195">
         <v>935.5</v>
@@ -16175,22 +16760,25 @@
       <c r="T195">
         <v>3147.9</v>
       </c>
-    </row>
-    <row r="196" spans="1:20">
+      <c r="U195">
+        <v>3348.6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21">
       <c r="A196" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B196" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C196" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D196" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E196" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F196">
         <v>264.6</v>
@@ -16237,22 +16825,25 @@
       <c r="T196">
         <v>7757.7</v>
       </c>
-    </row>
-    <row r="197" spans="1:20">
+      <c r="U196">
+        <v>11100.8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21">
       <c r="A197" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B197" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C197" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D197" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E197" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F197">
         <v>400.7</v>
@@ -16299,22 +16890,25 @@
       <c r="T197">
         <v>23900.1</v>
       </c>
-    </row>
-    <row r="198" spans="1:20">
+      <c r="U197">
+        <v>42671.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21">
       <c r="A198" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B198" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D198" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E198" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -16361,22 +16955,25 @@
       <c r="T198">
         <v>11438</v>
       </c>
-    </row>
-    <row r="199" spans="1:20">
+      <c r="U198">
+        <v>17117.3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21">
       <c r="A199" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B199" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C199" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D199" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E199" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F199">
         <v>244</v>
@@ -16423,22 +17020,25 @@
       <c r="T199">
         <v>3363.5</v>
       </c>
-    </row>
-    <row r="200" spans="1:20">
+      <c r="U199">
+        <v>3654.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21">
       <c r="A200" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B200" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C200" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D200" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E200" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F200">
         <v>176.1</v>
@@ -16485,22 +17085,25 @@
       <c r="T200">
         <v>5487.4</v>
       </c>
-    </row>
-    <row r="201" spans="1:20">
+      <c r="U200">
+        <v>5000.1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21">
       <c r="A201" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B201" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C201" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D201" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E201" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F201">
         <v>140.2</v>
@@ -16547,22 +17150,25 @@
       <c r="T201">
         <v>10348.6</v>
       </c>
-    </row>
-    <row r="202" spans="1:20">
+      <c r="U201">
+        <v>9030.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21">
       <c r="A202" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B202" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C202" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D202" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E202" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F202">
         <v>218.7</v>
@@ -16609,22 +17215,25 @@
       <c r="T202">
         <v>9789.9</v>
       </c>
-    </row>
-    <row r="203" spans="1:20">
+      <c r="U202">
+        <v>12422.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21">
       <c r="A203" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B203" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C203" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D203" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E203" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F203">
         <v>136.7</v>
@@ -16671,22 +17280,25 @@
       <c r="T203">
         <v>4428.8</v>
       </c>
-    </row>
-    <row r="204" spans="1:20">
+      <c r="U203">
+        <v>6629.9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21">
       <c r="A204" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B204" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C204" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D204" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E204" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -16733,22 +17345,25 @@
       <c r="T204">
         <v>11393</v>
       </c>
-    </row>
-    <row r="205" spans="1:20">
+      <c r="U204">
+        <v>17933.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21">
       <c r="A205" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B205" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C205" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D205" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E205" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F205">
         <v>167.6</v>
@@ -16795,22 +17410,25 @@
       <c r="T205">
         <v>3835.5</v>
       </c>
-    </row>
-    <row r="206" spans="1:20">
+      <c r="U205">
+        <v>4635.2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21">
       <c r="A206" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B206" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C206" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D206" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E206" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F206">
         <v>124</v>
@@ -16857,22 +17475,25 @@
       <c r="T206">
         <v>7257.2</v>
       </c>
-    </row>
-    <row r="207" spans="1:20">
+      <c r="U206">
+        <v>12847.3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21">
       <c r="A207" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B207" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C207" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D207" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E207" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F207">
         <v>210.7</v>
@@ -16919,22 +17540,25 @@
       <c r="T207">
         <v>2724.6</v>
       </c>
-    </row>
-    <row r="208" spans="1:20">
+      <c r="U207">
+        <v>7020.9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21">
       <c r="A208" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B208" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C208" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D208" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E208" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F208">
         <v>193</v>
@@ -16981,22 +17605,25 @@
       <c r="T208">
         <v>4665.4</v>
       </c>
-    </row>
-    <row r="209" spans="1:20">
+      <c r="U208">
+        <v>6817.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21">
       <c r="A209" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B209" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C209" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D209" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E209" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F209">
         <v>232.2</v>
@@ -17043,22 +17670,25 @@
       <c r="T209">
         <v>7817.7</v>
       </c>
-    </row>
-    <row r="210" spans="1:20">
+      <c r="U209">
+        <v>8305.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21">
       <c r="A210" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B210" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C210" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D210" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E210" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F210">
         <v>1472.4</v>
@@ -17105,22 +17735,25 @@
       <c r="T210">
         <v>29785.1</v>
       </c>
-    </row>
-    <row r="211" spans="1:20">
+      <c r="U210">
+        <v>37001.6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21">
       <c r="A211" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B211" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C211" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D211" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E211" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F211">
         <v>509.6</v>
@@ -17167,22 +17800,25 @@
       <c r="T211">
         <v>12021.8</v>
       </c>
-    </row>
-    <row r="212" spans="1:20">
+      <c r="U211">
+        <v>24710</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21">
       <c r="A212" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B212" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C212" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D212" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E212" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F212">
         <v>3887.5</v>
@@ -17229,22 +17865,25 @@
       <c r="T212">
         <v>45257.8</v>
       </c>
-    </row>
-    <row r="213" spans="1:20">
+      <c r="U212">
+        <v>81403</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21">
       <c r="A213" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B213" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C213" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D213" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E213" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F213">
         <v>2162.6</v>
@@ -17291,22 +17930,25 @@
       <c r="T213">
         <v>44557.1</v>
       </c>
-    </row>
-    <row r="214" spans="1:20">
+      <c r="U213">
+        <v>40221</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21">
       <c r="A214" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B214" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C214" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D214" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E214" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F214">
         <v>934.1</v>
@@ -17353,22 +17995,25 @@
       <c r="T214">
         <v>23511.8</v>
       </c>
-    </row>
-    <row r="215" spans="1:20">
+      <c r="U214">
+        <v>41479.7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21">
       <c r="A215" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B215" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C215" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D215" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E215" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F215">
         <v>4921.5</v>
@@ -17415,22 +18060,25 @@
       <c r="T215">
         <v>51193.2</v>
       </c>
-    </row>
-    <row r="216" spans="1:20">
+      <c r="U215">
+        <v>87173.5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21">
       <c r="A216" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B216" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C216" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D216" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E216" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F216">
         <v>953.5</v>
@@ -17477,22 +18125,25 @@
       <c r="T216">
         <v>42478.4</v>
       </c>
-    </row>
-    <row r="217" spans="1:20">
+      <c r="U216">
+        <v>34646.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:21">
       <c r="A217" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B217" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C217" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D217" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E217" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F217">
         <v>847.3</v>
@@ -17539,22 +18190,25 @@
       <c r="T217">
         <v>9321</v>
       </c>
-    </row>
-    <row r="218" spans="1:20">
+      <c r="U217">
+        <v>22680.8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21">
       <c r="A218" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B218" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C218" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D218" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E218" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F218">
         <v>1339.4</v>
@@ -17601,22 +18255,25 @@
       <c r="T218">
         <v>26736.7</v>
       </c>
-    </row>
-    <row r="219" spans="1:20">
+      <c r="U218">
+        <v>35167.6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21">
       <c r="A219" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B219" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C219" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D219" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E219" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F219">
         <v>2737.1</v>
@@ -17663,22 +18320,25 @@
       <c r="T219">
         <v>53465.5</v>
       </c>
-    </row>
-    <row r="220" spans="1:20">
+      <c r="U219">
+        <v>52481.4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21">
       <c r="A220" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B220" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C220" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D220" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E220" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F220">
         <v>1260.8</v>
@@ -17725,22 +18385,25 @@
       <c r="T220">
         <v>29398.1</v>
       </c>
-    </row>
-    <row r="221" spans="1:20">
+      <c r="U220">
+        <v>30463.5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21">
       <c r="A221" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B221" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C221" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D221" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E221" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -17787,22 +18450,25 @@
       <c r="T221">
         <v>23411.2</v>
       </c>
-    </row>
-    <row r="222" spans="1:20">
+      <c r="U221">
+        <v>27592.8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21">
       <c r="A222" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B222" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C222" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D222" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E222" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F222">
         <v>1183.9</v>
@@ -17848,6 +18514,9 @@
       </c>
       <c r="T222">
         <v>29077.3</v>
+      </c>
+      <c r="U222">
+        <v>33187.4</v>
       </c>
     </row>
   </sheetData>
@@ -17862,444 +18531,444 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="F2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B3" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="G3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B4" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C4" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D4" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B5" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D5" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E5" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F5" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G5" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H5" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B6" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C6" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E6" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F6" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G6" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B7" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C7" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D7" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F7" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G7" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H7" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B8" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C8" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D8" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E8" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F8" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G8" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H8" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B9" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C9" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E9" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F9" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G9" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H9" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B10" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C10" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D10" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E10" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G10" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H10" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B11" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C11" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E11" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F11" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G11" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H11" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B12" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C12" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E12" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="G12" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H12" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B13" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C13" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D13" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E13" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G13" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H13" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B14" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C14" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D14" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E14" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F14" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="G14" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H14" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B15" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C15" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D15" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E15" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F15" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G15" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H15" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B16" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C16" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D16" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E16" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F16" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G16" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H16" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B17" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C17" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D17" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E17" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F17" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G17" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H17" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
